--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9120" activeTab="1"/>
+    <workbookView windowWidth="21996" windowHeight="8507" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table" sheetId="2" r:id="rId1"/>
@@ -868,7 +868,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="150">
   <si>
     <t>Site</t>
   </si>
@@ -1336,6 +1336,9 @@
   </si>
   <si>
     <t xml:space="preserve">BTN_X3      </t>
+  </si>
+  <si>
+    <t>NUK-II</t>
   </si>
 </sst>
 </file>
@@ -1545,12 +1548,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
@@ -2380,7 +2383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2589,9 +2592,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2623,9 +2623,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2640,18 +2637,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2661,22 +2652,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2737,9 +2716,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3310,86 +3286,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:26">
-      <c r="A1" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="123" t="s">
+      <c r="A1" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="124" t="s">
+      <c r="D1" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="122" t="s">
+      <c r="E1" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="F1" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="124" t="s">
+      <c r="H1" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="122" t="s">
+      <c r="I1" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="123" t="s">
+      <c r="J1" s="114" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="123" t="s">
+      <c r="L1" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="123" t="s">
+      <c r="M1" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="131" t="s">
+      <c r="N1" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="131" t="s">
+      <c r="O1" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="122" t="s">
+      <c r="P1" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="153" t="s">
+      <c r="Q1" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="155" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="176"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="167"/>
     </row>
     <row r="2" ht="30.75" customHeight="1" spans="1:26">
-      <c r="A2" s="125"/>
+      <c r="A2" s="116"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="125"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="116"/>
       <c r="F2" s="66"/>
       <c r="G2" s="66"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="125"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="116"/>
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
       <c r="L2" s="66"/>
       <c r="M2" s="66"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="125"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="116"/>
       <c r="Q2" s="65" t="s">
         <v>18</v>
       </c>
@@ -3402,22 +3378,22 @@
       <c r="T2" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="122" t="s">
+      <c r="U2" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="123" t="s">
+      <c r="V2" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="123" t="s">
+      <c r="W2" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="X2" s="123" t="s">
+      <c r="X2" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" s="177" t="s">
+      <c r="Y2" s="168" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="178" t="s">
+      <c r="Z2" s="169" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3461,7 +3437,7 @@
       <c r="M3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="133" t="s">
+      <c r="N3" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -3470,7 +3446,7 @@
       <c r="P3" s="48">
         <v>0</v>
       </c>
-      <c r="Q3" s="157">
+      <c r="Q3" s="148">
         <v>0</v>
       </c>
       <c r="R3" s="11">
@@ -3482,12 +3458,12 @@
       <c r="T3" s="12">
         <v>0</v>
       </c>
-      <c r="U3" s="158"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="101"/>
-      <c r="Z3" s="102"/>
+      <c r="U3" s="149"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="94"/>
     </row>
     <row r="4" ht="15.15" spans="1:26">
       <c r="A4" s="54" t="s">
@@ -3529,7 +3505,7 @@
       <c r="M4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="134" t="s">
+      <c r="N4" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O4" s="12" t="s">
@@ -3538,7 +3514,7 @@
       <c r="P4" s="54">
         <v>0</v>
       </c>
-      <c r="Q4" s="159">
+      <c r="Q4" s="150">
         <v>0</v>
       </c>
       <c r="R4" s="7">
@@ -3550,15 +3526,15 @@
       <c r="T4" s="12">
         <v>0</v>
       </c>
-      <c r="U4" s="160"/>
-      <c r="V4" s="161"/>
-      <c r="W4" s="161"/>
-      <c r="X4" s="161"/>
-      <c r="Y4" s="161"/>
-      <c r="Z4" s="179"/>
+      <c r="U4" s="151"/>
+      <c r="V4" s="152"/>
+      <c r="W4" s="152"/>
+      <c r="X4" s="152"/>
+      <c r="Y4" s="152"/>
+      <c r="Z4" s="170"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:26">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="118" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3597,7 +3573,7 @@
       <c r="M5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="133" t="s">
+      <c r="N5" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -3606,7 +3582,7 @@
       <c r="P5" s="47">
         <v>1</v>
       </c>
-      <c r="Q5" s="162">
+      <c r="Q5" s="153">
         <v>0</v>
       </c>
       <c r="R5" s="3">
@@ -3618,17 +3594,17 @@
       <c r="T5" s="4">
         <v>0</v>
       </c>
-      <c r="U5" s="158"/>
-      <c r="V5" s="101"/>
-      <c r="W5" s="101" t="s">
+      <c r="U5" s="149"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="X5" s="101"/>
-      <c r="Y5" s="101"/>
-      <c r="Z5" s="102"/>
+      <c r="X5" s="93"/>
+      <c r="Y5" s="93"/>
+      <c r="Z5" s="94"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:26">
-      <c r="A6" s="128" t="s">
+      <c r="A6" s="119" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -3667,7 +3643,7 @@
       <c r="M6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="134" t="s">
+      <c r="N6" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="12" t="s">
@@ -3676,7 +3652,7 @@
       <c r="P6" s="48">
         <v>4</v>
       </c>
-      <c r="Q6" s="157">
+      <c r="Q6" s="148">
         <v>2</v>
       </c>
       <c r="R6" s="11">
@@ -3688,21 +3664,21 @@
       <c r="T6" s="12">
         <v>0</v>
       </c>
-      <c r="U6" s="163" t="s">
+      <c r="U6" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="V6" s="164" t="s">
+      <c r="V6" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="164" t="s">
+      <c r="W6" s="155" t="s">
         <v>36</v>
       </c>
-      <c r="X6" s="164"/>
-      <c r="Y6" s="164"/>
-      <c r="Z6" s="180"/>
+      <c r="X6" s="155"/>
+      <c r="Y6" s="155"/>
+      <c r="Z6" s="171"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:26">
-      <c r="A7" s="129" t="s">
+      <c r="A7" s="120" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3741,7 +3717,7 @@
       <c r="M7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="135" t="s">
+      <c r="N7" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O7" s="8" t="s">
@@ -3750,7 +3726,7 @@
       <c r="P7" s="54">
         <v>0</v>
       </c>
-      <c r="Q7" s="159">
+      <c r="Q7" s="150">
         <v>0</v>
       </c>
       <c r="R7" s="7">
@@ -3762,12 +3738,12 @@
       <c r="T7" s="8">
         <v>0</v>
       </c>
-      <c r="U7" s="160"/>
-      <c r="V7" s="161"/>
-      <c r="W7" s="161"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="161"/>
-      <c r="Z7" s="179"/>
+      <c r="U7" s="151"/>
+      <c r="V7" s="152"/>
+      <c r="W7" s="152"/>
+      <c r="X7" s="152"/>
+      <c r="Y7" s="152"/>
+      <c r="Z7" s="170"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="47" t="s">
@@ -3809,16 +3785,16 @@
       <c r="M8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="136" t="s">
+      <c r="N8" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="137" t="s">
+      <c r="O8" s="128" t="s">
         <v>40</v>
       </c>
       <c r="P8" s="47">
         <v>0</v>
       </c>
-      <c r="Q8" s="162">
+      <c r="Q8" s="153">
         <v>0</v>
       </c>
       <c r="R8" s="3">
@@ -3830,12 +3806,12 @@
       <c r="T8" s="4">
         <v>0</v>
       </c>
-      <c r="U8" s="158"/>
-      <c r="V8" s="101"/>
-      <c r="W8" s="101"/>
-      <c r="X8" s="101"/>
-      <c r="Y8" s="101"/>
-      <c r="Z8" s="102"/>
+      <c r="U8" s="149"/>
+      <c r="V8" s="93"/>
+      <c r="W8" s="93"/>
+      <c r="X8" s="93"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="94"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="48" t="s">
@@ -3877,16 +3853,16 @@
       <c r="M9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N9" s="134" t="s">
+      <c r="N9" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="137" t="s">
+      <c r="O9" s="128" t="s">
         <v>40</v>
       </c>
       <c r="P9" s="48">
         <v>0</v>
       </c>
-      <c r="Q9" s="157">
+      <c r="Q9" s="148">
         <v>0</v>
       </c>
       <c r="R9" s="11">
@@ -3898,12 +3874,12 @@
       <c r="T9" s="12">
         <v>0</v>
       </c>
-      <c r="U9" s="163"/>
-      <c r="V9" s="164"/>
-      <c r="W9" s="164"/>
-      <c r="X9" s="164"/>
-      <c r="Y9" s="164"/>
-      <c r="Z9" s="180"/>
+      <c r="U9" s="154"/>
+      <c r="V9" s="155"/>
+      <c r="W9" s="155"/>
+      <c r="X9" s="155"/>
+      <c r="Y9" s="155"/>
+      <c r="Z9" s="171"/>
     </row>
     <row r="10" ht="15.15" spans="1:26">
       <c r="A10" s="54" t="s">
@@ -3945,16 +3921,16 @@
       <c r="M10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N10" s="135" t="s">
+      <c r="N10" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="138" t="s">
+      <c r="O10" s="129" t="s">
         <v>40</v>
       </c>
       <c r="P10" s="54">
         <v>0</v>
       </c>
-      <c r="Q10" s="159">
+      <c r="Q10" s="150">
         <v>0</v>
       </c>
       <c r="R10" s="7">
@@ -3966,15 +3942,15 @@
       <c r="T10" s="8">
         <v>0</v>
       </c>
-      <c r="U10" s="160"/>
-      <c r="V10" s="161"/>
-      <c r="W10" s="161"/>
-      <c r="X10" s="161"/>
-      <c r="Y10" s="161"/>
-      <c r="Z10" s="179"/>
+      <c r="U10" s="151"/>
+      <c r="V10" s="152"/>
+      <c r="W10" s="152"/>
+      <c r="X10" s="152"/>
+      <c r="Y10" s="152"/>
+      <c r="Z10" s="170"/>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="127" t="s">
+      <c r="A11" s="118" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -4013,7 +3989,7 @@
       <c r="M11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="133" t="s">
+      <c r="N11" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O11" s="4" t="s">
@@ -4022,7 +3998,7 @@
       <c r="P11" s="47">
         <v>1</v>
       </c>
-      <c r="Q11" s="162">
+      <c r="Q11" s="153">
         <v>0</v>
       </c>
       <c r="R11" s="3">
@@ -4034,17 +4010,17 @@
       <c r="T11" s="4">
         <v>0</v>
       </c>
-      <c r="U11" s="158"/>
-      <c r="V11" s="101" t="s">
+      <c r="U11" s="149"/>
+      <c r="V11" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="W11" s="101"/>
-      <c r="X11" s="101"/>
-      <c r="Y11" s="101"/>
-      <c r="Z11" s="102"/>
+      <c r="W11" s="93"/>
+      <c r="X11" s="93"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="94"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="128" t="s">
+      <c r="A12" s="119" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -4083,7 +4059,7 @@
       <c r="M12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="134" t="s">
+      <c r="N12" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O12" s="12" t="s">
@@ -4092,7 +4068,7 @@
       <c r="P12" s="48">
         <v>0</v>
       </c>
-      <c r="Q12" s="157">
+      <c r="Q12" s="148">
         <v>0</v>
       </c>
       <c r="R12" s="11">
@@ -4104,15 +4080,15 @@
       <c r="T12" s="12">
         <v>0</v>
       </c>
-      <c r="U12" s="163"/>
-      <c r="V12" s="164"/>
-      <c r="W12" s="164"/>
-      <c r="X12" s="164"/>
-      <c r="Y12" s="164"/>
-      <c r="Z12" s="180"/>
+      <c r="U12" s="154"/>
+      <c r="V12" s="155"/>
+      <c r="W12" s="155"/>
+      <c r="X12" s="155"/>
+      <c r="Y12" s="155"/>
+      <c r="Z12" s="171"/>
     </row>
     <row r="13" ht="15.15" spans="1:26">
-      <c r="A13" s="128" t="s">
+      <c r="A13" s="119" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -4151,7 +4127,7 @@
       <c r="M13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N13" s="135" t="s">
+      <c r="N13" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -4160,7 +4136,7 @@
       <c r="P13" s="54">
         <v>0</v>
       </c>
-      <c r="Q13" s="159">
+      <c r="Q13" s="150">
         <v>0</v>
       </c>
       <c r="R13" s="7">
@@ -4172,15 +4148,15 @@
       <c r="T13" s="8">
         <v>0</v>
       </c>
-      <c r="U13" s="160"/>
-      <c r="V13" s="161"/>
-      <c r="W13" s="161"/>
-      <c r="X13" s="161"/>
-      <c r="Y13" s="161"/>
-      <c r="Z13" s="179"/>
+      <c r="U13" s="151"/>
+      <c r="V13" s="152"/>
+      <c r="W13" s="152"/>
+      <c r="X13" s="152"/>
+      <c r="Y13" s="152"/>
+      <c r="Z13" s="170"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:26">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="118" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -4216,19 +4192,19 @@
       <c r="L14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="139" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="140" t="s">
+      <c r="M14" s="130" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="O14" s="139" t="s">
+      <c r="O14" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="P14" s="80">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="81">
+      <c r="P14" s="79">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="80">
         <v>0</v>
       </c>
       <c r="R14" s="23">
@@ -4240,15 +4216,15 @@
       <c r="T14" s="49">
         <v>0</v>
       </c>
-      <c r="U14" s="165"/>
-      <c r="V14" s="166"/>
-      <c r="W14" s="166"/>
-      <c r="X14" s="166"/>
-      <c r="Y14" s="166"/>
-      <c r="Z14" s="181"/>
+      <c r="U14" s="156"/>
+      <c r="V14" s="157"/>
+      <c r="W14" s="157"/>
+      <c r="X14" s="157"/>
+      <c r="Y14" s="157"/>
+      <c r="Z14" s="172"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:26">
-      <c r="A15" s="128" t="s">
+      <c r="A15" s="119" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -4287,40 +4263,40 @@
       <c r="M15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N15" s="134" t="s">
+      <c r="N15" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="88">
+      <c r="P15" s="85">
         <v>2</v>
       </c>
-      <c r="Q15" s="89">
+      <c r="Q15" s="86">
         <v>0</v>
       </c>
       <c r="R15" s="24">
         <v>1</v>
       </c>
-      <c r="S15" s="167">
-        <v>1</v>
-      </c>
-      <c r="T15" s="151">
-        <v>0</v>
-      </c>
-      <c r="U15" s="163"/>
-      <c r="V15" s="164" t="s">
+      <c r="S15" s="158">
+        <v>1</v>
+      </c>
+      <c r="T15" s="142">
+        <v>0</v>
+      </c>
+      <c r="U15" s="154"/>
+      <c r="V15" s="155" t="s">
         <v>49</v>
       </c>
-      <c r="W15" s="164" t="s">
+      <c r="W15" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="X15" s="164"/>
-      <c r="Y15" s="164"/>
-      <c r="Z15" s="180"/>
+      <c r="X15" s="155"/>
+      <c r="Y15" s="155"/>
+      <c r="Z15" s="171"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="128" t="s">
+      <c r="A16" s="119" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -4359,16 +4335,16 @@
       <c r="M16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N16" s="134" t="s">
+      <c r="N16" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="157">
+      <c r="P16" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="148">
         <v>0</v>
       </c>
       <c r="R16" s="11">
@@ -4380,15 +4356,15 @@
       <c r="T16" s="12">
         <v>0</v>
       </c>
-      <c r="U16" s="163"/>
-      <c r="V16" s="164"/>
-      <c r="W16" s="164"/>
-      <c r="X16" s="164"/>
-      <c r="Y16" s="164"/>
-      <c r="Z16" s="180"/>
+      <c r="U16" s="154"/>
+      <c r="V16" s="155"/>
+      <c r="W16" s="155"/>
+      <c r="X16" s="155"/>
+      <c r="Y16" s="155"/>
+      <c r="Z16" s="171"/>
     </row>
     <row r="17" ht="15.15" spans="1:26">
-      <c r="A17" s="129" t="s">
+      <c r="A17" s="120" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -4427,16 +4403,16 @@
       <c r="M17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N17" s="135" t="s">
+      <c r="N17" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P17" s="141">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="159">
+      <c r="P17" s="132">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="150">
         <v>0</v>
       </c>
       <c r="R17" s="7">
@@ -4448,15 +4424,15 @@
       <c r="T17" s="8">
         <v>0</v>
       </c>
-      <c r="U17" s="160"/>
-      <c r="V17" s="161"/>
-      <c r="W17" s="161"/>
-      <c r="X17" s="161"/>
-      <c r="Y17" s="161"/>
-      <c r="Z17" s="179"/>
+      <c r="U17" s="151"/>
+      <c r="V17" s="152"/>
+      <c r="W17" s="152"/>
+      <c r="X17" s="152"/>
+      <c r="Y17" s="152"/>
+      <c r="Z17" s="170"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:26">
-      <c r="A18" s="128" t="s">
+      <c r="A18" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="18" t="s">
@@ -4495,16 +4471,16 @@
       <c r="M18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N18" s="133" t="s">
+      <c r="N18" s="124" t="s">
         <v>47</v>
       </c>
       <c r="O18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P18" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="86">
+      <c r="P18" s="83">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="84">
         <v>0</v>
       </c>
       <c r="R18" s="34">
@@ -4516,17 +4492,17 @@
       <c r="T18" s="35">
         <v>0</v>
       </c>
-      <c r="U18" s="158"/>
-      <c r="V18" s="101">
+      <c r="U18" s="149"/>
+      <c r="V18" s="93">
         <v>52</v>
       </c>
-      <c r="W18" s="101"/>
-      <c r="X18" s="101"/>
-      <c r="Y18" s="101"/>
-      <c r="Z18" s="102"/>
+      <c r="W18" s="93"/>
+      <c r="X18" s="93"/>
+      <c r="Y18" s="93"/>
+      <c r="Z18" s="94"/>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="128" t="s">
+      <c r="A19" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="18" t="s">
@@ -4565,16 +4541,16 @@
       <c r="M19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N19" s="142" t="s">
+      <c r="N19" s="133" t="s">
         <v>54</v>
       </c>
       <c r="O19" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="P19" s="88">
+      <c r="P19" s="85">
         <v>4</v>
       </c>
-      <c r="Q19" s="89">
+      <c r="Q19" s="86">
         <v>2</v>
       </c>
       <c r="R19" s="24">
@@ -4586,21 +4562,21 @@
       <c r="T19" s="40">
         <v>0</v>
       </c>
-      <c r="U19" s="163" t="s">
+      <c r="U19" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="V19" s="164">
+      <c r="V19" s="155">
         <v>13</v>
       </c>
-      <c r="W19" s="164">
+      <c r="W19" s="155">
         <v>49</v>
       </c>
-      <c r="X19" s="164"/>
-      <c r="Y19" s="164"/>
-      <c r="Z19" s="180"/>
+      <c r="X19" s="155"/>
+      <c r="Y19" s="155"/>
+      <c r="Z19" s="171"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="128" t="s">
+      <c r="A20" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="18" t="s">
@@ -4636,41 +4612,41 @@
       <c r="L20" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="143" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="144" t="s">
+      <c r="M20" s="134" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="O20" s="145" t="s">
+      <c r="O20" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="P20" s="91">
+      <c r="P20" s="87">
         <v>2</v>
       </c>
-      <c r="Q20" s="92">
+      <c r="Q20" s="88">
         <v>2</v>
       </c>
-      <c r="R20" s="94">
-        <v>0</v>
-      </c>
-      <c r="S20" s="94">
+      <c r="R20" s="89">
+        <v>0</v>
+      </c>
+      <c r="S20" s="89">
         <v>0</v>
       </c>
       <c r="T20" s="38">
         <v>0</v>
       </c>
-      <c r="U20" s="168" t="s">
+      <c r="U20" s="159" t="s">
         <v>58</v>
       </c>
-      <c r="V20" s="103"/>
-      <c r="W20" s="103"/>
-      <c r="X20" s="103"/>
-      <c r="Y20" s="103"/>
-      <c r="Z20" s="104"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="96"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="128" t="s">
+      <c r="A21" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="18" t="s">
@@ -4709,16 +4685,16 @@
       <c r="M21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N21" s="134" t="s">
+      <c r="N21" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="88">
+      <c r="P21" s="85">
         <v>3</v>
       </c>
-      <c r="Q21" s="89">
+      <c r="Q21" s="86">
         <v>0</v>
       </c>
       <c r="R21" s="24">
@@ -4730,19 +4706,19 @@
       <c r="T21" s="12">
         <v>1</v>
       </c>
-      <c r="U21" s="163"/>
-      <c r="V21" s="164"/>
-      <c r="W21" s="164"/>
-      <c r="X21" s="164" t="s">
+      <c r="U21" s="154"/>
+      <c r="V21" s="155"/>
+      <c r="W21" s="155"/>
+      <c r="X21" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="Y21" s="164" t="s">
+      <c r="Y21" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="Z21" s="180"/>
+      <c r="Z21" s="171"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="128" t="s">
+      <c r="A22" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -4781,16 +4757,16 @@
       <c r="M22" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N22" s="134" t="s">
+      <c r="N22" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P22" s="88">
+      <c r="P22" s="85">
         <v>3</v>
       </c>
-      <c r="Q22" s="89">
+      <c r="Q22" s="86">
         <v>0</v>
       </c>
       <c r="R22" s="24">
@@ -4802,19 +4778,19 @@
       <c r="T22" s="12">
         <v>0</v>
       </c>
-      <c r="U22" s="163"/>
-      <c r="V22" s="164"/>
-      <c r="W22" s="164" t="s">
+      <c r="U22" s="154"/>
+      <c r="V22" s="155"/>
+      <c r="W22" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="X22" s="164"/>
-      <c r="Y22" s="164" t="s">
+      <c r="X22" s="155"/>
+      <c r="Y22" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="Z22" s="180"/>
+      <c r="Z22" s="171"/>
     </row>
     <row r="23" ht="15.15" spans="1:26">
-      <c r="A23" s="128" t="s">
+      <c r="A23" s="119" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="18" t="s">
@@ -4853,16 +4829,16 @@
       <c r="M23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N23" s="135" t="s">
+      <c r="N23" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P23" s="88">
+      <c r="P23" s="85">
         <v>5</v>
       </c>
-      <c r="Q23" s="89">
+      <c r="Q23" s="86">
         <v>0</v>
       </c>
       <c r="R23" s="24">
@@ -4874,19 +4850,19 @@
       <c r="T23" s="12">
         <v>0</v>
       </c>
-      <c r="U23" s="160"/>
-      <c r="V23" s="161"/>
-      <c r="W23" s="169" t="s">
+      <c r="U23" s="151"/>
+      <c r="V23" s="152"/>
+      <c r="W23" s="160" t="s">
         <v>63</v>
       </c>
-      <c r="X23" s="161"/>
-      <c r="Y23" s="161" t="s">
+      <c r="X23" s="152"/>
+      <c r="Y23" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="Z23" s="179"/>
+      <c r="Z23" s="170"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:26">
-      <c r="A24" s="130" t="s">
+      <c r="A24" s="121" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="30" t="s">
@@ -4925,16 +4901,16 @@
       <c r="M24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="140" t="s">
+      <c r="N24" s="131" t="s">
         <v>47</v>
       </c>
       <c r="O24" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="95">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="96">
+      <c r="P24" s="90">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="91">
         <v>0</v>
       </c>
       <c r="R24" s="57">
@@ -4946,14 +4922,14 @@
       <c r="T24" s="58">
         <v>0</v>
       </c>
-      <c r="U24" s="170"/>
-      <c r="V24" s="113">
-        <v>29</v>
-      </c>
-      <c r="W24" s="113"/>
-      <c r="X24" s="113"/>
-      <c r="Y24" s="113"/>
-      <c r="Z24" s="114"/>
+      <c r="U24" s="161"/>
+      <c r="V24" s="105">
+        <v>29</v>
+      </c>
+      <c r="W24" s="105"/>
+      <c r="X24" s="105"/>
+      <c r="Y24" s="105"/>
+      <c r="Z24" s="106"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="47" t="s">
@@ -4995,16 +4971,16 @@
       <c r="M25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N25" s="133" t="s">
+      <c r="N25" s="124" t="s">
         <v>47</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P25" s="85">
+      <c r="P25" s="83">
         <v>2</v>
       </c>
-      <c r="Q25" s="86">
+      <c r="Q25" s="84">
         <v>1</v>
       </c>
       <c r="R25" s="34">
@@ -5016,16 +4992,16 @@
       <c r="T25" s="35">
         <v>0</v>
       </c>
-      <c r="U25" s="158">
+      <c r="U25" s="149">
         <v>43</v>
       </c>
-      <c r="V25" s="101">
+      <c r="V25" s="93">
         <v>20</v>
       </c>
-      <c r="W25" s="101"/>
-      <c r="X25" s="101"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="102"/>
+      <c r="W25" s="93"/>
+      <c r="X25" s="93"/>
+      <c r="Y25" s="93"/>
+      <c r="Z25" s="94"/>
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="48" t="s">
@@ -5067,39 +5043,39 @@
       <c r="M26" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="N26" s="144" t="s">
+      <c r="N26" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="O26" s="145" t="s">
+      <c r="O26" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="P26" s="91">
+      <c r="P26" s="87">
         <v>6</v>
       </c>
-      <c r="Q26" s="92">
-        <v>1</v>
-      </c>
-      <c r="R26" s="94">
+      <c r="Q26" s="88">
+        <v>1</v>
+      </c>
+      <c r="R26" s="89">
         <v>3</v>
       </c>
-      <c r="S26" s="94">
+      <c r="S26" s="89">
         <v>2</v>
       </c>
       <c r="T26" s="38">
         <v>0</v>
       </c>
-      <c r="U26" s="168">
+      <c r="U26" s="159">
         <v>30</v>
       </c>
-      <c r="V26" s="103" t="s">
+      <c r="V26" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="W26" s="103" t="s">
+      <c r="W26" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="X26" s="103"/>
-      <c r="Y26" s="103"/>
-      <c r="Z26" s="104"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="96"/>
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="48" t="s">
@@ -5141,16 +5117,16 @@
       <c r="M27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N27" s="134" t="s">
+      <c r="N27" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P27" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="89">
+      <c r="P27" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="86">
         <v>0</v>
       </c>
       <c r="R27" s="24">
@@ -5162,12 +5138,12 @@
       <c r="T27" s="40">
         <v>0</v>
       </c>
-      <c r="U27" s="163"/>
-      <c r="V27" s="164"/>
-      <c r="W27" s="164"/>
-      <c r="X27" s="164"/>
-      <c r="Y27" s="164"/>
-      <c r="Z27" s="180"/>
+      <c r="U27" s="154"/>
+      <c r="V27" s="155"/>
+      <c r="W27" s="155"/>
+      <c r="X27" s="155"/>
+      <c r="Y27" s="155"/>
+      <c r="Z27" s="171"/>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="48" t="s">
@@ -5209,16 +5185,16 @@
       <c r="M28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N28" s="134" t="s">
+      <c r="N28" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P28" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="89">
+      <c r="P28" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="86">
         <v>0</v>
       </c>
       <c r="R28" s="24">
@@ -5230,12 +5206,12 @@
       <c r="T28" s="40">
         <v>0</v>
       </c>
-      <c r="U28" s="163"/>
-      <c r="V28" s="164"/>
-      <c r="W28" s="164"/>
-      <c r="X28" s="164"/>
-      <c r="Y28" s="164"/>
-      <c r="Z28" s="180"/>
+      <c r="U28" s="154"/>
+      <c r="V28" s="155"/>
+      <c r="W28" s="155"/>
+      <c r="X28" s="155"/>
+      <c r="Y28" s="155"/>
+      <c r="Z28" s="171"/>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="48" t="s">
@@ -5277,16 +5253,16 @@
       <c r="M29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N29" s="134" t="s">
+      <c r="N29" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O29" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P29" s="88">
+      <c r="P29" s="85">
         <v>2</v>
       </c>
-      <c r="Q29" s="89">
+      <c r="Q29" s="86">
         <v>1</v>
       </c>
       <c r="R29" s="24">
@@ -5298,16 +5274,16 @@
       <c r="T29" s="40">
         <v>0</v>
       </c>
-      <c r="U29" s="163" t="s">
+      <c r="U29" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="V29" s="164" t="s">
+      <c r="V29" s="155" t="s">
         <v>72</v>
       </c>
-      <c r="W29" s="164"/>
-      <c r="X29" s="164"/>
-      <c r="Y29" s="164"/>
-      <c r="Z29" s="180"/>
+      <c r="W29" s="155"/>
+      <c r="X29" s="155"/>
+      <c r="Y29" s="155"/>
+      <c r="Z29" s="171"/>
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="48" t="s">
@@ -5349,16 +5325,16 @@
       <c r="M30" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N30" s="134" t="s">
+      <c r="N30" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P30" s="88">
+      <c r="P30" s="85">
         <v>2</v>
       </c>
-      <c r="Q30" s="89">
+      <c r="Q30" s="86">
         <v>0</v>
       </c>
       <c r="R30" s="24">
@@ -5370,16 +5346,16 @@
       <c r="T30" s="12">
         <v>0</v>
       </c>
-      <c r="U30" s="163"/>
-      <c r="V30" s="164" t="s">
+      <c r="U30" s="154"/>
+      <c r="V30" s="155" t="s">
         <v>74</v>
       </c>
-      <c r="W30" s="164" t="s">
+      <c r="W30" s="155" t="s">
         <v>75</v>
       </c>
-      <c r="X30" s="164"/>
-      <c r="Y30" s="164"/>
-      <c r="Z30" s="180"/>
+      <c r="X30" s="155"/>
+      <c r="Y30" s="155"/>
+      <c r="Z30" s="171"/>
     </row>
     <row r="31" ht="15.15" spans="1:26">
       <c r="A31" s="48" t="s">
@@ -5421,16 +5397,16 @@
       <c r="M31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N31" s="135" t="s">
+      <c r="N31" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O31" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="P31" s="141">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="171">
+      <c r="P31" s="132">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="162">
         <v>1</v>
       </c>
       <c r="R31" s="25">
@@ -5442,17 +5418,17 @@
       <c r="T31" s="8">
         <v>0</v>
       </c>
-      <c r="U31" s="160" t="s">
+      <c r="U31" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="V31" s="161"/>
-      <c r="W31" s="161"/>
-      <c r="X31" s="161"/>
-      <c r="Y31" s="161"/>
-      <c r="Z31" s="179"/>
+      <c r="V31" s="152"/>
+      <c r="W31" s="152"/>
+      <c r="X31" s="152"/>
+      <c r="Y31" s="152"/>
+      <c r="Z31" s="170"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:26">
-      <c r="A32" s="127" t="s">
+      <c r="A32" s="118" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -5491,16 +5467,16 @@
       <c r="M32" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N32" s="133" t="s">
+      <c r="N32" s="124" t="s">
         <v>47</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P32" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="86">
+      <c r="P32" s="83">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="84">
         <v>1</v>
       </c>
       <c r="R32" s="34">
@@ -5512,17 +5488,17 @@
       <c r="T32" s="35">
         <v>0</v>
       </c>
-      <c r="U32" s="158">
+      <c r="U32" s="149">
         <v>59</v>
       </c>
-      <c r="V32" s="101"/>
-      <c r="W32" s="101"/>
-      <c r="X32" s="101"/>
-      <c r="Y32" s="101"/>
-      <c r="Z32" s="102"/>
+      <c r="V32" s="93"/>
+      <c r="W32" s="93"/>
+      <c r="X32" s="93"/>
+      <c r="Y32" s="93"/>
+      <c r="Z32" s="94"/>
     </row>
     <row r="33" ht="15.15" spans="1:26">
-      <c r="A33" s="129" t="s">
+      <c r="A33" s="120" t="s">
         <v>78</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -5561,16 +5537,16 @@
       <c r="M33" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N33" s="146" t="s">
+      <c r="N33" s="137" t="s">
         <v>54</v>
       </c>
-      <c r="O33" s="147" t="s">
+      <c r="O33" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="P33" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="89">
+      <c r="P33" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="86">
         <v>0</v>
       </c>
       <c r="R33" s="24">
@@ -5582,15 +5558,15 @@
       <c r="T33" s="40">
         <v>0</v>
       </c>
-      <c r="U33" s="160"/>
-      <c r="V33" s="161"/>
-      <c r="W33" s="161"/>
-      <c r="X33" s="161"/>
-      <c r="Y33" s="161"/>
-      <c r="Z33" s="179"/>
+      <c r="U33" s="151"/>
+      <c r="V33" s="152"/>
+      <c r="W33" s="152"/>
+      <c r="X33" s="152"/>
+      <c r="Y33" s="152"/>
+      <c r="Z33" s="170"/>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="128" t="s">
+      <c r="A34" s="119" t="s">
         <v>80</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -5629,16 +5605,16 @@
       <c r="M34" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N34" s="140" t="s">
+      <c r="N34" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="O34" s="139" t="s">
+      <c r="O34" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="P34" s="80">
+      <c r="P34" s="79">
         <v>3</v>
       </c>
-      <c r="Q34" s="81">
+      <c r="Q34" s="80">
         <v>1</v>
       </c>
       <c r="R34" s="23">
@@ -5650,19 +5626,19 @@
       <c r="T34" s="49">
         <v>0</v>
       </c>
-      <c r="U34" s="165">
+      <c r="U34" s="156">
         <v>41</v>
       </c>
-      <c r="V34" s="166"/>
-      <c r="W34" s="166"/>
-      <c r="X34" s="166"/>
-      <c r="Y34" s="166" t="s">
+      <c r="V34" s="157"/>
+      <c r="W34" s="157"/>
+      <c r="X34" s="157"/>
+      <c r="Y34" s="157" t="s">
         <v>82</v>
       </c>
-      <c r="Z34" s="181"/>
+      <c r="Z34" s="172"/>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="128" t="s">
+      <c r="A35" s="119" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="11" t="s">
@@ -5686,7 +5662,7 @@
       <c r="H35" s="46">
         <v>32</v>
       </c>
-      <c r="I35" s="148" t="s">
+      <c r="I35" s="139" t="s">
         <v>29</v>
       </c>
       <c r="J35" s="26" t="s">
@@ -5701,16 +5677,16 @@
       <c r="M35" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="N35" s="134" t="s">
+      <c r="N35" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="O35" s="149" t="s">
+      <c r="O35" s="140" t="s">
         <v>48</v>
       </c>
-      <c r="P35" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="89">
+      <c r="P35" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="86">
         <v>0</v>
       </c>
       <c r="R35" s="24">
@@ -5722,17 +5698,17 @@
       <c r="T35" s="12">
         <v>0</v>
       </c>
-      <c r="U35" s="163"/>
-      <c r="V35" s="164"/>
-      <c r="W35" s="164"/>
-      <c r="X35" s="164"/>
-      <c r="Y35" s="164" t="s">
+      <c r="U35" s="154"/>
+      <c r="V35" s="155"/>
+      <c r="W35" s="155"/>
+      <c r="X35" s="155"/>
+      <c r="Y35" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="Z35" s="180"/>
+      <c r="Z35" s="171"/>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="128" t="s">
+      <c r="A36" s="119" t="s">
         <v>80</v>
       </c>
       <c r="B36" s="11" t="s">
@@ -5771,16 +5747,16 @@
       <c r="M36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N36" s="134" t="s">
+      <c r="N36" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P36" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="89">
+      <c r="P36" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="86">
         <v>1</v>
       </c>
       <c r="R36" s="24">
@@ -5792,17 +5768,17 @@
       <c r="T36" s="12">
         <v>0</v>
       </c>
-      <c r="U36" s="163" t="s">
+      <c r="U36" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="V36" s="164"/>
-      <c r="W36" s="164"/>
-      <c r="X36" s="164"/>
-      <c r="Y36" s="164"/>
-      <c r="Z36" s="180"/>
+      <c r="V36" s="155"/>
+      <c r="W36" s="155"/>
+      <c r="X36" s="155"/>
+      <c r="Y36" s="155"/>
+      <c r="Z36" s="171"/>
     </row>
     <row r="37" ht="15.15" spans="1:26">
-      <c r="A37" s="129" t="s">
+      <c r="A37" s="120" t="s">
         <v>80</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -5841,16 +5817,16 @@
       <c r="M37" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N37" s="135" t="s">
+      <c r="N37" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O37" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P37" s="141">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="171">
+      <c r="P37" s="132">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="162">
         <v>0</v>
       </c>
       <c r="R37" s="25">
@@ -5862,12 +5838,12 @@
       <c r="T37" s="8">
         <v>0</v>
       </c>
-      <c r="U37" s="160"/>
-      <c r="V37" s="161"/>
-      <c r="W37" s="161"/>
-      <c r="X37" s="161"/>
-      <c r="Y37" s="161"/>
-      <c r="Z37" s="179"/>
+      <c r="U37" s="151"/>
+      <c r="V37" s="152"/>
+      <c r="W37" s="152"/>
+      <c r="X37" s="152"/>
+      <c r="Y37" s="152"/>
+      <c r="Z37" s="170"/>
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="47" t="s">
@@ -5909,16 +5885,16 @@
       <c r="M38" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N38" s="133" t="s">
+      <c r="N38" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P38" s="85">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="162">
+      <c r="P38" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="153">
         <v>0</v>
       </c>
       <c r="R38" s="3">
@@ -5930,12 +5906,12 @@
       <c r="T38" s="4">
         <v>0</v>
       </c>
-      <c r="U38" s="158"/>
-      <c r="V38" s="101"/>
-      <c r="W38" s="101"/>
-      <c r="X38" s="101"/>
-      <c r="Y38" s="101"/>
-      <c r="Z38" s="102"/>
+      <c r="U38" s="149"/>
+      <c r="V38" s="93"/>
+      <c r="W38" s="93"/>
+      <c r="X38" s="93"/>
+      <c r="Y38" s="93"/>
+      <c r="Z38" s="94"/>
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="48" t="s">
@@ -5977,16 +5953,16 @@
       <c r="M39" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N39" s="134" t="s">
+      <c r="N39" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P39" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="157">
+      <c r="P39" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="148">
         <v>0</v>
       </c>
       <c r="R39" s="11">
@@ -5998,12 +5974,12 @@
       <c r="T39" s="12">
         <v>0</v>
       </c>
-      <c r="U39" s="163"/>
-      <c r="V39" s="164"/>
-      <c r="W39" s="164"/>
-      <c r="X39" s="164"/>
-      <c r="Y39" s="164"/>
-      <c r="Z39" s="180"/>
+      <c r="U39" s="154"/>
+      <c r="V39" s="155"/>
+      <c r="W39" s="155"/>
+      <c r="X39" s="155"/>
+      <c r="Y39" s="155"/>
+      <c r="Z39" s="171"/>
     </row>
     <row r="40" ht="15.15" spans="1:26">
       <c r="A40" s="48" t="s">
@@ -6045,16 +6021,16 @@
       <c r="M40" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N40" s="135" t="s">
+      <c r="N40" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P40" s="141">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="159">
+      <c r="P40" s="132">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="150">
         <v>0</v>
       </c>
       <c r="R40" s="7">
@@ -6066,15 +6042,15 @@
       <c r="T40" s="8">
         <v>0</v>
       </c>
-      <c r="U40" s="160"/>
-      <c r="V40" s="161"/>
-      <c r="W40" s="161"/>
-      <c r="X40" s="161"/>
-      <c r="Y40" s="161"/>
-      <c r="Z40" s="179"/>
+      <c r="U40" s="151"/>
+      <c r="V40" s="152"/>
+      <c r="W40" s="152"/>
+      <c r="X40" s="152"/>
+      <c r="Y40" s="152"/>
+      <c r="Z40" s="170"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="127" t="s">
+      <c r="A41" s="118" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -6113,16 +6089,16 @@
       <c r="M41" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N41" s="140" t="s">
+      <c r="N41" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="O41" s="139" t="s">
+      <c r="O41" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="P41" s="80">
+      <c r="P41" s="79">
         <v>3</v>
       </c>
-      <c r="Q41" s="81">
+      <c r="Q41" s="80">
         <v>3</v>
       </c>
       <c r="R41" s="23">
@@ -6134,17 +6110,17 @@
       <c r="T41" s="49">
         <v>0</v>
       </c>
-      <c r="U41" s="165" t="s">
+      <c r="U41" s="156" t="s">
         <v>89</v>
       </c>
-      <c r="V41" s="166"/>
-      <c r="W41" s="166"/>
-      <c r="X41" s="166"/>
-      <c r="Y41" s="166"/>
-      <c r="Z41" s="181"/>
+      <c r="V41" s="157"/>
+      <c r="W41" s="157"/>
+      <c r="X41" s="157"/>
+      <c r="Y41" s="157"/>
+      <c r="Z41" s="172"/>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="128" t="s">
+      <c r="A42" s="119" t="s">
         <v>87</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -6183,16 +6159,16 @@
       <c r="M42" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N42" s="134" t="s">
+      <c r="N42" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P42" s="88">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="89">
+      <c r="P42" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="86">
         <v>0</v>
       </c>
       <c r="R42" s="24">
@@ -6204,15 +6180,15 @@
       <c r="T42" s="40">
         <v>0</v>
       </c>
-      <c r="U42" s="163"/>
-      <c r="V42" s="164"/>
-      <c r="W42" s="164"/>
-      <c r="X42" s="164"/>
-      <c r="Y42" s="164"/>
-      <c r="Z42" s="180"/>
+      <c r="U42" s="154"/>
+      <c r="V42" s="155"/>
+      <c r="W42" s="155"/>
+      <c r="X42" s="155"/>
+      <c r="Y42" s="155"/>
+      <c r="Z42" s="171"/>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="128" t="s">
+      <c r="A43" s="119" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="11" t="s">
@@ -6251,16 +6227,16 @@
       <c r="M43" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N43" s="134" t="s">
+      <c r="N43" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O43" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P43" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="89">
+      <c r="P43" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="86">
         <v>1</v>
       </c>
       <c r="R43" s="24">
@@ -6272,17 +6248,17 @@
       <c r="T43" s="40">
         <v>0</v>
       </c>
-      <c r="U43" s="163" t="s">
+      <c r="U43" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="V43" s="164"/>
-      <c r="W43" s="164"/>
-      <c r="X43" s="164"/>
-      <c r="Y43" s="164"/>
-      <c r="Z43" s="180"/>
+      <c r="V43" s="155"/>
+      <c r="W43" s="155"/>
+      <c r="X43" s="155"/>
+      <c r="Y43" s="155"/>
+      <c r="Z43" s="171"/>
     </row>
     <row r="44" ht="15.15" spans="1:26">
-      <c r="A44" s="129" t="s">
+      <c r="A44" s="120" t="s">
         <v>87</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -6321,16 +6297,16 @@
       <c r="M44" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N44" s="135" t="s">
+      <c r="N44" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O44" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P44" s="141">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="171">
+      <c r="P44" s="132">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="162">
         <v>0</v>
       </c>
       <c r="R44" s="25">
@@ -6342,17 +6318,17 @@
       <c r="T44" s="44">
         <v>0</v>
       </c>
-      <c r="U44" s="160"/>
-      <c r="V44" s="161" t="s">
+      <c r="U44" s="151"/>
+      <c r="V44" s="152" t="s">
         <v>90</v>
       </c>
-      <c r="W44" s="161"/>
-      <c r="X44" s="161"/>
-      <c r="Y44" s="161"/>
-      <c r="Z44" s="179"/>
+      <c r="W44" s="152"/>
+      <c r="X44" s="152"/>
+      <c r="Y44" s="152"/>
+      <c r="Z44" s="170"/>
     </row>
     <row r="45" ht="15.15" spans="1:26">
-      <c r="A45" s="130" t="s">
+      <c r="A45" s="121" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="55" t="s">
@@ -6376,7 +6352,7 @@
       <c r="H45" s="58">
         <v>64</v>
       </c>
-      <c r="I45" s="111" t="s">
+      <c r="I45" s="103" t="s">
         <v>29</v>
       </c>
       <c r="J45" s="55" t="s">
@@ -6391,16 +6367,16 @@
       <c r="M45" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="N45" s="150" t="s">
+      <c r="N45" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="O45" s="110" t="s">
+      <c r="O45" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="P45" s="95">
+      <c r="P45" s="90">
         <v>6</v>
       </c>
-      <c r="Q45" s="96">
+      <c r="Q45" s="91">
         <v>3</v>
       </c>
       <c r="R45" s="57">
@@ -6412,18 +6388,18 @@
       <c r="T45" s="58">
         <v>0</v>
       </c>
-      <c r="U45" s="170" t="s">
+      <c r="U45" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="V45" s="113" t="s">
+      <c r="V45" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="W45" s="113">
+      <c r="W45" s="105">
         <v>32</v>
       </c>
-      <c r="X45" s="113"/>
-      <c r="Y45" s="113"/>
-      <c r="Z45" s="114"/>
+      <c r="X45" s="105"/>
+      <c r="Y45" s="105"/>
+      <c r="Z45" s="106"/>
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="48" t="s">
@@ -6465,16 +6441,16 @@
       <c r="M46" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N46" s="133" t="s">
+      <c r="N46" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O46" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P46" s="85">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="86">
+      <c r="P46" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="84">
         <v>0</v>
       </c>
       <c r="R46" s="34">
@@ -6486,12 +6462,12 @@
       <c r="T46" s="4">
         <v>0</v>
       </c>
-      <c r="U46" s="158"/>
-      <c r="V46" s="101"/>
-      <c r="W46" s="101"/>
-      <c r="X46" s="101"/>
-      <c r="Y46" s="101"/>
-      <c r="Z46" s="102"/>
+      <c r="U46" s="149"/>
+      <c r="V46" s="93"/>
+      <c r="W46" s="93"/>
+      <c r="X46" s="93"/>
+      <c r="Y46" s="93"/>
+      <c r="Z46" s="94"/>
     </row>
     <row r="47" spans="1:26">
       <c r="A47" s="48" t="s">
@@ -6533,16 +6509,16 @@
       <c r="M47" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N47" s="134" t="s">
+      <c r="N47" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O47" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P47" s="88">
+      <c r="P47" s="85">
         <v>7</v>
       </c>
-      <c r="Q47" s="89">
+      <c r="Q47" s="86">
         <v>4</v>
       </c>
       <c r="R47" s="24">
@@ -6554,18 +6530,18 @@
       <c r="T47" s="12">
         <v>0</v>
       </c>
-      <c r="U47" s="172" t="s">
+      <c r="U47" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="V47" s="164" t="s">
+      <c r="V47" s="155" t="s">
         <v>98</v>
       </c>
-      <c r="W47" s="164" t="s">
+      <c r="W47" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="X47" s="164"/>
-      <c r="Y47" s="164"/>
-      <c r="Z47" s="180"/>
+      <c r="X47" s="155"/>
+      <c r="Y47" s="155"/>
+      <c r="Z47" s="171"/>
     </row>
     <row r="48" ht="15.15" spans="1:26">
       <c r="A48" s="54" t="s">
@@ -6607,16 +6583,16 @@
       <c r="M48" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N48" s="135" t="s">
+      <c r="N48" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O48" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P48" s="141">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="171">
+      <c r="P48" s="132">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="162">
         <v>1</v>
       </c>
       <c r="R48" s="25">
@@ -6628,14 +6604,14 @@
       <c r="T48" s="8">
         <v>0</v>
       </c>
-      <c r="U48" s="160" t="s">
+      <c r="U48" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="V48" s="161"/>
-      <c r="W48" s="161"/>
-      <c r="X48" s="161"/>
-      <c r="Y48" s="161"/>
-      <c r="Z48" s="179"/>
+      <c r="V48" s="152"/>
+      <c r="W48" s="152"/>
+      <c r="X48" s="152"/>
+      <c r="Y48" s="152"/>
+      <c r="Z48" s="170"/>
     </row>
     <row r="49" spans="1:26">
       <c r="A49" s="47" t="s">
@@ -6677,16 +6653,16 @@
       <c r="M49" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N49" s="133" t="s">
+      <c r="N49" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O49" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P49" s="85">
+      <c r="P49" s="83">
         <v>4</v>
       </c>
-      <c r="Q49" s="86">
+      <c r="Q49" s="84">
         <v>3</v>
       </c>
       <c r="R49" s="34">
@@ -6698,16 +6674,16 @@
       <c r="T49" s="4">
         <v>0</v>
       </c>
-      <c r="U49" s="158" t="s">
+      <c r="U49" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="V49" s="101"/>
-      <c r="W49" s="101"/>
-      <c r="X49" s="101"/>
-      <c r="Y49" s="101" t="s">
+      <c r="V49" s="93"/>
+      <c r="W49" s="93"/>
+      <c r="X49" s="93"/>
+      <c r="Y49" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="Z49" s="102"/>
+      <c r="Z49" s="94"/>
     </row>
     <row r="50" spans="1:26">
       <c r="A50" s="48" t="s">
@@ -6749,16 +6725,16 @@
       <c r="M50" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N50" s="134" t="s">
+      <c r="N50" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O50" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P50" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="89">
+      <c r="P50" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="86">
         <v>0</v>
       </c>
       <c r="R50" s="24">
@@ -6770,14 +6746,14 @@
       <c r="T50" s="12">
         <v>0</v>
       </c>
-      <c r="U50" s="163"/>
-      <c r="V50" s="164" t="s">
+      <c r="U50" s="154"/>
+      <c r="V50" s="155" t="s">
         <v>105</v>
       </c>
-      <c r="W50" s="164"/>
-      <c r="X50" s="164"/>
-      <c r="Y50" s="164"/>
-      <c r="Z50" s="180"/>
+      <c r="W50" s="155"/>
+      <c r="X50" s="155"/>
+      <c r="Y50" s="155"/>
+      <c r="Z50" s="171"/>
     </row>
     <row r="51" ht="15.15" spans="1:26">
       <c r="A51" s="54" t="s">
@@ -6819,16 +6795,16 @@
       <c r="M51" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N51" s="135" t="s">
+      <c r="N51" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O51" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P51" s="141">
+      <c r="P51" s="132">
         <v>2</v>
       </c>
-      <c r="Q51" s="171">
+      <c r="Q51" s="162">
         <v>1</v>
       </c>
       <c r="R51" s="25">
@@ -6840,19 +6816,19 @@
       <c r="T51" s="8">
         <v>0</v>
       </c>
-      <c r="U51" s="160" t="s">
+      <c r="U51" s="151" t="s">
         <v>106</v>
       </c>
-      <c r="V51" s="161"/>
-      <c r="W51" s="161"/>
-      <c r="X51" s="161"/>
-      <c r="Y51" s="161" t="s">
+      <c r="V51" s="152"/>
+      <c r="W51" s="152"/>
+      <c r="X51" s="152"/>
+      <c r="Y51" s="152" t="s">
         <v>107</v>
       </c>
-      <c r="Z51" s="179"/>
+      <c r="Z51" s="170"/>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:26">
-      <c r="A52" s="127" t="s">
+      <c r="A52" s="118" t="s">
         <v>108</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -6891,16 +6867,16 @@
       <c r="M52" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N52" s="133" t="s">
+      <c r="N52" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O52" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P52" s="85">
+      <c r="P52" s="83">
         <v>6</v>
       </c>
-      <c r="Q52" s="86">
+      <c r="Q52" s="84">
         <v>4</v>
       </c>
       <c r="R52" s="34">
@@ -6912,21 +6888,21 @@
       <c r="T52" s="4">
         <v>0</v>
       </c>
-      <c r="U52" s="173" t="s">
+      <c r="U52" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="V52" s="101" t="s">
+      <c r="V52" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="W52" s="101" t="s">
+      <c r="W52" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="X52" s="101"/>
-      <c r="Y52" s="101"/>
-      <c r="Z52" s="102"/>
+      <c r="X52" s="93"/>
+      <c r="Y52" s="93"/>
+      <c r="Z52" s="94"/>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="128" t="s">
+      <c r="A53" s="119" t="s">
         <v>108</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -6965,16 +6941,16 @@
       <c r="M53" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N53" s="134" t="s">
+      <c r="N53" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O53" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P53" s="88">
+      <c r="P53" s="85">
         <v>2</v>
       </c>
-      <c r="Q53" s="89">
+      <c r="Q53" s="86">
         <v>0</v>
       </c>
       <c r="R53" s="24">
@@ -6986,19 +6962,19 @@
       <c r="T53" s="12">
         <v>0</v>
       </c>
-      <c r="U53" s="163"/>
-      <c r="V53" s="164"/>
-      <c r="W53" s="164" t="s">
+      <c r="U53" s="154"/>
+      <c r="V53" s="155"/>
+      <c r="W53" s="155" t="s">
         <v>112</v>
       </c>
-      <c r="X53" s="164"/>
-      <c r="Y53" s="164" t="s">
+      <c r="X53" s="155"/>
+      <c r="Y53" s="155" t="s">
         <v>113</v>
       </c>
-      <c r="Z53" s="180"/>
+      <c r="Z53" s="171"/>
     </row>
     <row r="54" ht="15.15" spans="1:26">
-      <c r="A54" s="129" t="s">
+      <c r="A54" s="120" t="s">
         <v>108</v>
       </c>
       <c r="B54" s="7" t="s">
@@ -7037,16 +7013,16 @@
       <c r="M54" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N54" s="135" t="s">
+      <c r="N54" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O54" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P54" s="141">
+      <c r="P54" s="132">
         <v>3</v>
       </c>
-      <c r="Q54" s="171">
+      <c r="Q54" s="162">
         <v>3</v>
       </c>
       <c r="R54" s="25">
@@ -7058,14 +7034,14 @@
       <c r="T54" s="8">
         <v>0</v>
       </c>
-      <c r="U54" s="160" t="s">
+      <c r="U54" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="V54" s="161"/>
-      <c r="W54" s="161"/>
-      <c r="X54" s="161"/>
-      <c r="Y54" s="161"/>
-      <c r="Z54" s="179"/>
+      <c r="V54" s="152"/>
+      <c r="W54" s="152"/>
+      <c r="X54" s="152"/>
+      <c r="Y54" s="152"/>
+      <c r="Z54" s="170"/>
     </row>
     <row r="55" spans="1:26">
       <c r="A55" s="47" t="s">
@@ -7107,16 +7083,16 @@
       <c r="M55" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N55" s="133" t="s">
+      <c r="N55" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O55" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P55" s="85">
+      <c r="P55" s="83">
         <v>2</v>
       </c>
-      <c r="Q55" s="86">
+      <c r="Q55" s="84">
         <v>0</v>
       </c>
       <c r="R55" s="34">
@@ -7128,16 +7104,16 @@
       <c r="T55" s="4">
         <v>0</v>
       </c>
-      <c r="U55" s="158"/>
-      <c r="V55" s="101" t="s">
+      <c r="U55" s="149"/>
+      <c r="V55" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="W55" s="101"/>
-      <c r="X55" s="101"/>
-      <c r="Y55" s="101" t="s">
+      <c r="W55" s="93"/>
+      <c r="X55" s="93"/>
+      <c r="Y55" s="93" t="s">
         <v>117</v>
       </c>
-      <c r="Z55" s="102"/>
+      <c r="Z55" s="94"/>
     </row>
     <row r="56" spans="1:26">
       <c r="A56" s="48" t="s">
@@ -7179,16 +7155,16 @@
       <c r="M56" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N56" s="134" t="s">
+      <c r="N56" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O56" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P56" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="89">
+      <c r="P56" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="86">
         <v>0</v>
       </c>
       <c r="R56" s="24">
@@ -7200,14 +7176,14 @@
       <c r="T56" s="12">
         <v>0</v>
       </c>
-      <c r="U56" s="163"/>
-      <c r="V56" s="164" t="s">
+      <c r="U56" s="154"/>
+      <c r="V56" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="W56" s="164"/>
-      <c r="X56" s="164"/>
-      <c r="Y56" s="164"/>
-      <c r="Z56" s="180"/>
+      <c r="W56" s="155"/>
+      <c r="X56" s="155"/>
+      <c r="Y56" s="155"/>
+      <c r="Z56" s="171"/>
     </row>
     <row r="57" ht="15.15" spans="1:26">
       <c r="A57" s="54" t="s">
@@ -7249,16 +7225,16 @@
       <c r="M57" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N57" s="135" t="s">
+      <c r="N57" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O57" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P57" s="141">
+      <c r="P57" s="132">
         <v>5</v>
       </c>
-      <c r="Q57" s="171">
+      <c r="Q57" s="162">
         <v>1</v>
       </c>
       <c r="R57" s="25">
@@ -7270,21 +7246,21 @@
       <c r="T57" s="8">
         <v>0</v>
       </c>
-      <c r="U57" s="160" t="s">
+      <c r="U57" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="V57" s="161" t="s">
+      <c r="V57" s="152" t="s">
         <v>120</v>
       </c>
-      <c r="W57" s="161"/>
-      <c r="X57" s="161"/>
-      <c r="Y57" s="161" t="s">
+      <c r="W57" s="152"/>
+      <c r="X57" s="152"/>
+      <c r="Y57" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="Z57" s="179"/>
+      <c r="Z57" s="170"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="127" t="s">
+      <c r="A58" s="118" t="s">
         <v>122</v>
       </c>
       <c r="B58" s="59" t="s">
@@ -7323,16 +7299,16 @@
       <c r="M58" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N58" s="133" t="s">
+      <c r="N58" s="124" t="s">
         <v>28</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P58" s="85">
+      <c r="P58" s="83">
         <v>6</v>
       </c>
-      <c r="Q58" s="86">
+      <c r="Q58" s="84">
         <v>2</v>
       </c>
       <c r="R58" s="34">
@@ -7344,23 +7320,23 @@
       <c r="T58" s="4">
         <v>0</v>
       </c>
-      <c r="U58" s="158" t="s">
+      <c r="U58" s="149" t="s">
         <v>124</v>
       </c>
-      <c r="V58" s="101" t="s">
+      <c r="V58" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="W58" s="101" t="s">
+      <c r="W58" s="93" t="s">
         <v>126</v>
       </c>
-      <c r="X58" s="101"/>
-      <c r="Y58" s="101" t="s">
+      <c r="X58" s="93"/>
+      <c r="Y58" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="Z58" s="102"/>
+      <c r="Z58" s="94"/>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="128" t="s">
+      <c r="A59" s="119" t="s">
         <v>122</v>
       </c>
       <c r="B59" s="61" t="s">
@@ -7399,16 +7375,16 @@
       <c r="M59" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N59" s="134" t="s">
+      <c r="N59" s="125" t="s">
         <v>28</v>
       </c>
       <c r="O59" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P59" s="88">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="89">
+      <c r="P59" s="85">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="86">
         <v>0</v>
       </c>
       <c r="R59" s="24">
@@ -7420,17 +7396,17 @@
       <c r="T59" s="12">
         <v>0</v>
       </c>
-      <c r="U59" s="163"/>
-      <c r="V59" s="164"/>
-      <c r="W59" s="164" t="s">
+      <c r="U59" s="154"/>
+      <c r="V59" s="155"/>
+      <c r="W59" s="155" t="s">
         <v>128</v>
       </c>
-      <c r="X59" s="164"/>
-      <c r="Y59" s="164"/>
-      <c r="Z59" s="180"/>
+      <c r="X59" s="155"/>
+      <c r="Y59" s="155"/>
+      <c r="Z59" s="171"/>
     </row>
     <row r="60" ht="15.15" spans="1:26">
-      <c r="A60" s="128" t="s">
+      <c r="A60" s="119" t="s">
         <v>122</v>
       </c>
       <c r="B60" s="61" t="s">
@@ -7469,16 +7445,16 @@
       <c r="M60" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N60" s="135" t="s">
+      <c r="N60" s="126" t="s">
         <v>28</v>
       </c>
       <c r="O60" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P60" s="141">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="171">
+      <c r="P60" s="132">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="162">
         <v>1</v>
       </c>
       <c r="R60" s="25">
@@ -7490,14 +7466,14 @@
       <c r="T60" s="8">
         <v>0</v>
       </c>
-      <c r="U60" s="160" t="s">
+      <c r="U60" s="151" t="s">
         <v>129</v>
       </c>
-      <c r="V60" s="161"/>
-      <c r="W60" s="161"/>
-      <c r="X60" s="161"/>
-      <c r="Y60" s="161"/>
-      <c r="Z60" s="179"/>
+      <c r="V60" s="152"/>
+      <c r="W60" s="152"/>
+      <c r="X60" s="152"/>
+      <c r="Y60" s="152"/>
+      <c r="Z60" s="170"/>
     </row>
     <row r="61" spans="1:26">
       <c r="A61" s="47" t="s">
@@ -7539,37 +7515,37 @@
       <c r="M61" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N61" s="133" t="s">
+      <c r="N61" s="124" t="s">
         <v>47</v>
       </c>
       <c r="O61" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P61" s="85">
+      <c r="P61" s="83">
         <v>2</v>
       </c>
-      <c r="Q61" s="86">
+      <c r="Q61" s="84">
         <v>1</v>
       </c>
       <c r="R61" s="34">
         <v>1</v>
       </c>
-      <c r="S61" s="101">
-        <v>0</v>
-      </c>
-      <c r="T61" s="102">
-        <v>0</v>
-      </c>
-      <c r="U61" s="158">
+      <c r="S61" s="93">
+        <v>0</v>
+      </c>
+      <c r="T61" s="94">
+        <v>0</v>
+      </c>
+      <c r="U61" s="149">
         <v>56</v>
       </c>
-      <c r="V61" s="101">
+      <c r="V61" s="93">
         <v>43</v>
       </c>
-      <c r="W61" s="101"/>
-      <c r="X61" s="101"/>
-      <c r="Y61" s="101"/>
-      <c r="Z61" s="102"/>
+      <c r="W61" s="93"/>
+      <c r="X61" s="93"/>
+      <c r="Y61" s="93"/>
+      <c r="Z61" s="94"/>
     </row>
     <row r="62" ht="20.4" spans="1:26">
       <c r="A62" s="48" t="s">
@@ -7611,16 +7587,16 @@
       <c r="M62" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N62" s="142" t="s">
+      <c r="N62" s="133" t="s">
         <v>54</v>
       </c>
       <c r="O62" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="P62" s="88">
+      <c r="P62" s="85">
         <v>12</v>
       </c>
-      <c r="Q62" s="89">
+      <c r="Q62" s="86">
         <v>9</v>
       </c>
       <c r="R62" s="24">
@@ -7632,7 +7608,7 @@
       <c r="T62" s="12">
         <v>0</v>
       </c>
-      <c r="U62" s="174" t="s">
+      <c r="U62" s="165" t="s">
         <v>132</v>
       </c>
       <c r="V62" s="11" t="s">
@@ -7685,39 +7661,39 @@
       <c r="M63" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="N63" s="144" t="s">
+      <c r="N63" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="O63" s="145" t="s">
+      <c r="O63" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="P63" s="91">
+      <c r="P63" s="87">
         <v>5</v>
       </c>
-      <c r="Q63" s="92">
+      <c r="Q63" s="88">
         <v>2</v>
       </c>
-      <c r="R63" s="94">
-        <v>1</v>
-      </c>
-      <c r="S63" s="103">
+      <c r="R63" s="89">
+        <v>1</v>
+      </c>
+      <c r="S63" s="95">
         <v>2</v>
       </c>
-      <c r="T63" s="104">
-        <v>0</v>
-      </c>
-      <c r="U63" s="168" t="s">
+      <c r="T63" s="96">
+        <v>0</v>
+      </c>
+      <c r="U63" s="159" t="s">
         <v>134</v>
       </c>
-      <c r="V63" s="103">
+      <c r="V63" s="95">
         <v>320</v>
       </c>
-      <c r="W63" s="103" t="s">
+      <c r="W63" s="95" t="s">
         <v>135</v>
       </c>
-      <c r="X63" s="103"/>
-      <c r="Y63" s="103"/>
-      <c r="Z63" s="104"/>
+      <c r="X63" s="95"/>
+      <c r="Y63" s="95"/>
+      <c r="Z63" s="96"/>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:26">
       <c r="A64" s="48" t="s">
@@ -7759,16 +7735,16 @@
       <c r="M64" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N64" s="142" t="s">
+      <c r="N64" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="O64" s="151" t="s">
+      <c r="O64" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="P64" s="152">
+      <c r="P64" s="143">
         <v>5</v>
       </c>
-      <c r="Q64" s="175">
+      <c r="Q64" s="166">
         <v>1</v>
       </c>
       <c r="R64" s="18">
@@ -7780,16 +7756,16 @@
       <c r="T64" s="64">
         <v>0</v>
       </c>
-      <c r="U64" s="163">
+      <c r="U64" s="154">
         <v>23</v>
       </c>
-      <c r="V64" s="164" t="s">
+      <c r="V64" s="155" t="s">
         <v>136</v>
       </c>
-      <c r="W64" s="164"/>
-      <c r="X64" s="164"/>
-      <c r="Y64" s="164"/>
-      <c r="Z64" s="180">
+      <c r="W64" s="155"/>
+      <c r="X64" s="155"/>
+      <c r="Y64" s="155"/>
+      <c r="Z64" s="171">
         <v>9</v>
       </c>
     </row>
@@ -7833,16 +7809,16 @@
       <c r="M65" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="N65" s="142" t="s">
+      <c r="N65" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="O65" s="151" t="s">
+      <c r="O65" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="P65" s="152">
+      <c r="P65" s="143">
         <v>3</v>
       </c>
-      <c r="Q65" s="175">
+      <c r="Q65" s="166">
         <v>1</v>
       </c>
       <c r="R65" s="18">
@@ -7854,14 +7830,14 @@
       <c r="T65" s="64">
         <v>0</v>
       </c>
-      <c r="U65" s="163">
+      <c r="U65" s="154">
         <v>80</v>
       </c>
-      <c r="V65" s="164"/>
-      <c r="W65" s="164"/>
-      <c r="X65" s="164"/>
-      <c r="Y65" s="164"/>
-      <c r="Z65" s="180" t="s">
+      <c r="V65" s="155"/>
+      <c r="W65" s="155"/>
+      <c r="X65" s="155"/>
+      <c r="Y65" s="155"/>
+      <c r="Z65" s="171" t="s">
         <v>137</v>
       </c>
     </row>
@@ -7887,7 +7863,7 @@
       <c r="G66" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H66" s="147">
+      <c r="H66" s="138">
         <v>54</v>
       </c>
       <c r="I66" s="54" t="s">
@@ -7905,16 +7881,16 @@
       <c r="M66" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N66" s="182" t="s">
+      <c r="N66" s="173" t="s">
         <v>28</v>
       </c>
-      <c r="O66" s="183" t="s">
+      <c r="O66" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="P66" s="184">
+      <c r="P66" s="175">
         <v>7</v>
       </c>
-      <c r="Q66" s="185">
+      <c r="Q66" s="176">
         <v>2</v>
       </c>
       <c r="R66" s="19">
@@ -7923,24 +7899,24 @@
       <c r="S66" s="19">
         <v>0</v>
       </c>
-      <c r="T66" s="147">
-        <v>0</v>
-      </c>
-      <c r="U66" s="160" t="s">
+      <c r="T66" s="138">
+        <v>0</v>
+      </c>
+      <c r="U66" s="151" t="s">
         <v>138</v>
       </c>
-      <c r="V66" s="161"/>
-      <c r="W66" s="161"/>
-      <c r="X66" s="161"/>
-      <c r="Y66" s="161">
+      <c r="V66" s="152"/>
+      <c r="W66" s="152"/>
+      <c r="X66" s="152"/>
+      <c r="Y66" s="152">
         <v>150</v>
       </c>
-      <c r="Z66" s="186" t="s">
+      <c r="Z66" s="177" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="67" ht="15.15" spans="1:26">
-      <c r="A67" s="130" t="s">
+      <c r="A67" s="121" t="s">
         <v>140</v>
       </c>
       <c r="B67" s="55" t="s">
@@ -7949,10 +7925,10 @@
       <c r="C67" s="55">
         <v>59.56098</v>
       </c>
-      <c r="D67" s="110">
+      <c r="D67" s="102">
         <v>150.924676</v>
       </c>
-      <c r="E67" s="111">
+      <c r="E67" s="103">
         <v>2021</v>
       </c>
       <c r="F67" s="56">
@@ -7961,10 +7937,10 @@
       <c r="G67" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="110">
+      <c r="H67" s="102">
         <v>64</v>
       </c>
-      <c r="I67" s="111" t="s">
+      <c r="I67" s="103" t="s">
         <v>29</v>
       </c>
       <c r="J67" s="55" t="s">
@@ -7979,16 +7955,16 @@
       <c r="M67" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="N67" s="150" t="s">
+      <c r="N67" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="O67" s="110" t="s">
+      <c r="O67" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="P67" s="111">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="119">
+      <c r="P67" s="103">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="111">
         <v>1</v>
       </c>
       <c r="R67" s="55">
@@ -7997,32 +7973,32 @@
       <c r="S67" s="55">
         <v>0</v>
       </c>
-      <c r="T67" s="110">
-        <v>0</v>
-      </c>
-      <c r="U67" s="170">
+      <c r="T67" s="102">
+        <v>0</v>
+      </c>
+      <c r="U67" s="161">
         <v>7</v>
       </c>
-      <c r="V67" s="113"/>
-      <c r="W67" s="113"/>
-      <c r="X67" s="113"/>
-      <c r="Y67" s="113"/>
-      <c r="Z67" s="114"/>
+      <c r="V67" s="105"/>
+      <c r="W67" s="105"/>
+      <c r="X67" s="105"/>
+      <c r="Y67" s="105"/>
+      <c r="Z67" s="106"/>
     </row>
     <row r="68" ht="15.15" spans="1:26">
-      <c r="A68" s="170" t="s">
+      <c r="A68" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="113" t="s">
+      <c r="B68" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="C68" s="113">
+      <c r="C68" s="105">
         <v>59.558174</v>
       </c>
-      <c r="D68" s="114">
+      <c r="D68" s="106">
         <v>150.929357</v>
       </c>
-      <c r="E68" s="111">
+      <c r="E68" s="103">
         <v>2021</v>
       </c>
       <c r="F68" s="56">
@@ -8031,10 +8007,10 @@
       <c r="G68" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="H68" s="110">
+      <c r="H68" s="102">
         <v>64</v>
       </c>
-      <c r="I68" s="111" t="s">
+      <c r="I68" s="103" t="s">
         <v>29</v>
       </c>
       <c r="J68" s="55" t="s">
@@ -8049,16 +8025,16 @@
       <c r="M68" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="N68" s="150" t="s">
+      <c r="N68" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="O68" s="110" t="s">
+      <c r="O68" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="P68" s="111">
+      <c r="P68" s="103">
         <v>2</v>
       </c>
-      <c r="Q68" s="119">
+      <c r="Q68" s="111">
         <v>1</v>
       </c>
       <c r="R68" s="55">
@@ -8067,17 +8043,17 @@
       <c r="S68" s="30">
         <v>0</v>
       </c>
-      <c r="T68" s="121">
-        <v>0</v>
-      </c>
-      <c r="U68" s="170">
+      <c r="T68" s="112">
+        <v>0</v>
+      </c>
+      <c r="U68" s="161">
         <v>12</v>
       </c>
-      <c r="V68" s="113"/>
-      <c r="W68" s="113"/>
-      <c r="X68" s="113"/>
-      <c r="Y68" s="113"/>
-      <c r="Z68" s="114">
+      <c r="V68" s="105"/>
+      <c r="W68" s="105"/>
+      <c r="X68" s="105"/>
+      <c r="Y68" s="105"/>
+      <c r="Z68" s="106">
         <v>7</v>
       </c>
     </row>
@@ -8114,7 +8090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:N67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -8201,13 +8177,13 @@
       <c r="K2" s="69">
         <v>0</v>
       </c>
-      <c r="L2" s="70">
-        <v>0</v>
-      </c>
-      <c r="M2" s="70">
-        <v>0</v>
-      </c>
-      <c r="N2" s="71">
+      <c r="L2" s="69">
+        <v>0</v>
+      </c>
+      <c r="M2" s="69">
+        <v>0</v>
+      </c>
+      <c r="N2" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8236,22 +8212,22 @@
       <c r="H3" s="7">
         <v>48</v>
       </c>
-      <c r="I3" s="72">
-        <v>0</v>
-      </c>
-      <c r="J3" s="73">
+      <c r="I3" s="71">
+        <v>0</v>
+      </c>
+      <c r="J3" s="72">
         <v>0</v>
       </c>
       <c r="K3" s="69">
         <v>0</v>
       </c>
-      <c r="L3" s="74">
-        <v>0</v>
-      </c>
-      <c r="M3" s="74">
-        <v>0</v>
-      </c>
-      <c r="N3" s="71">
+      <c r="L3" s="73">
+        <v>0</v>
+      </c>
+      <c r="M3" s="73">
+        <v>0</v>
+      </c>
+      <c r="N3" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8280,22 +8256,22 @@
       <c r="H4" s="3">
         <v>32</v>
       </c>
-      <c r="I4" s="75">
-        <v>1</v>
-      </c>
-      <c r="J4" s="76">
+      <c r="I4" s="74">
+        <v>1</v>
+      </c>
+      <c r="J4" s="75">
         <v>0</v>
       </c>
       <c r="K4" s="69">
         <v>0</v>
       </c>
-      <c r="L4" s="77">
-        <v>0</v>
-      </c>
-      <c r="M4" s="77">
-        <v>1</v>
-      </c>
-      <c r="N4" s="78">
+      <c r="L4" s="76">
+        <v>0</v>
+      </c>
+      <c r="M4" s="76">
+        <v>1</v>
+      </c>
+      <c r="N4" s="77">
         <v>0</v>
       </c>
     </row>
@@ -8333,13 +8309,13 @@
       <c r="K5" s="69">
         <v>0</v>
       </c>
-      <c r="L5" s="70">
-        <v>1</v>
-      </c>
-      <c r="M5" s="70">
-        <v>1</v>
-      </c>
-      <c r="N5" s="71">
+      <c r="L5" s="69">
+        <v>1</v>
+      </c>
+      <c r="M5" s="69">
+        <v>1</v>
+      </c>
+      <c r="N5" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8368,22 +8344,22 @@
       <c r="H6" s="7">
         <v>32</v>
       </c>
-      <c r="I6" s="72">
-        <v>0</v>
-      </c>
-      <c r="J6" s="73">
+      <c r="I6" s="71">
+        <v>0</v>
+      </c>
+      <c r="J6" s="72">
         <v>0</v>
       </c>
       <c r="K6" s="69">
         <v>0</v>
       </c>
-      <c r="L6" s="74">
-        <v>0</v>
-      </c>
-      <c r="M6" s="74">
-        <v>0</v>
-      </c>
-      <c r="N6" s="79">
+      <c r="L6" s="73">
+        <v>0</v>
+      </c>
+      <c r="M6" s="73">
+        <v>0</v>
+      </c>
+      <c r="N6" s="78">
         <v>0</v>
       </c>
     </row>
@@ -8412,22 +8388,22 @@
       <c r="H7" s="16">
         <v>96</v>
       </c>
-      <c r="I7" s="75">
-        <v>0</v>
-      </c>
-      <c r="J7" s="76">
+      <c r="I7" s="74">
+        <v>0</v>
+      </c>
+      <c r="J7" s="75">
         <v>0</v>
       </c>
       <c r="K7" s="69">
         <v>0</v>
       </c>
-      <c r="L7" s="77">
-        <v>0</v>
-      </c>
-      <c r="M7" s="77">
-        <v>0</v>
-      </c>
-      <c r="N7" s="78">
+      <c r="L7" s="76">
+        <v>0</v>
+      </c>
+      <c r="M7" s="76">
+        <v>0</v>
+      </c>
+      <c r="N7" s="77">
         <v>0</v>
       </c>
     </row>
@@ -8465,13 +8441,13 @@
       <c r="K8" s="69">
         <v>0</v>
       </c>
-      <c r="L8" s="70">
-        <v>0</v>
-      </c>
-      <c r="M8" s="70">
-        <v>0</v>
-      </c>
-      <c r="N8" s="71">
+      <c r="L8" s="69">
+        <v>0</v>
+      </c>
+      <c r="M8" s="69">
+        <v>0</v>
+      </c>
+      <c r="N8" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8500,22 +8476,22 @@
       <c r="H9" s="19">
         <v>64</v>
       </c>
-      <c r="I9" s="72">
-        <v>0</v>
-      </c>
-      <c r="J9" s="73">
+      <c r="I9" s="71">
+        <v>0</v>
+      </c>
+      <c r="J9" s="72">
         <v>0</v>
       </c>
       <c r="K9" s="69">
         <v>0</v>
       </c>
-      <c r="L9" s="74">
-        <v>0</v>
-      </c>
-      <c r="M9" s="74">
-        <v>0</v>
-      </c>
-      <c r="N9" s="79">
+      <c r="L9" s="73">
+        <v>0</v>
+      </c>
+      <c r="M9" s="73">
+        <v>0</v>
+      </c>
+      <c r="N9" s="78">
         <v>0</v>
       </c>
     </row>
@@ -8544,22 +8520,22 @@
       <c r="H10" s="3">
         <v>32</v>
       </c>
-      <c r="I10" s="75">
-        <v>1</v>
-      </c>
-      <c r="J10" s="76">
+      <c r="I10" s="74">
+        <v>1</v>
+      </c>
+      <c r="J10" s="75">
         <v>0</v>
       </c>
       <c r="K10" s="69">
         <v>0</v>
       </c>
-      <c r="L10" s="77">
-        <v>1</v>
-      </c>
-      <c r="M10" s="77">
-        <v>0</v>
-      </c>
-      <c r="N10" s="78">
+      <c r="L10" s="76">
+        <v>1</v>
+      </c>
+      <c r="M10" s="76">
+        <v>0</v>
+      </c>
+      <c r="N10" s="77">
         <v>0</v>
       </c>
     </row>
@@ -8597,13 +8573,13 @@
       <c r="K11" s="69">
         <v>0</v>
       </c>
-      <c r="L11" s="70">
-        <v>0</v>
-      </c>
-      <c r="M11" s="70">
-        <v>0</v>
-      </c>
-      <c r="N11" s="71">
+      <c r="L11" s="69">
+        <v>0</v>
+      </c>
+      <c r="M11" s="69">
+        <v>0</v>
+      </c>
+      <c r="N11" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8632,26 +8608,26 @@
       <c r="H12" s="11">
         <v>32</v>
       </c>
-      <c r="I12" s="72">
-        <v>0</v>
-      </c>
-      <c r="J12" s="73">
+      <c r="I12" s="71">
+        <v>0</v>
+      </c>
+      <c r="J12" s="72">
         <v>0</v>
       </c>
       <c r="K12" s="69">
         <v>0</v>
       </c>
-      <c r="L12" s="74">
-        <v>0</v>
-      </c>
-      <c r="M12" s="74">
-        <v>0</v>
-      </c>
-      <c r="N12" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="28.8" hidden="1" spans="1:14">
+      <c r="L12" s="73">
+        <v>0</v>
+      </c>
+      <c r="M12" s="73">
+        <v>0</v>
+      </c>
+      <c r="N12" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:14">
       <c r="A13" s="9" t="s">
         <v>44</v>
       </c>
@@ -8676,13 +8652,13 @@
       <c r="H13" s="23">
         <v>64</v>
       </c>
-      <c r="I13" s="80">
-        <v>0</v>
-      </c>
-      <c r="J13" s="81">
-        <v>0</v>
-      </c>
-      <c r="K13" s="82"/>
+      <c r="I13" s="79">
+        <v>0</v>
+      </c>
+      <c r="J13" s="80">
+        <v>0</v>
+      </c>
+      <c r="K13" s="23"/>
       <c r="L13" s="23">
         <v>0</v>
       </c>
@@ -8727,13 +8703,13 @@
       <c r="K14" s="69">
         <v>0</v>
       </c>
-      <c r="L14" s="70">
-        <v>1</v>
-      </c>
-      <c r="M14" s="83">
-        <v>1</v>
-      </c>
-      <c r="N14" s="84">
+      <c r="L14" s="69">
+        <v>1</v>
+      </c>
+      <c r="M14" s="81">
+        <v>1</v>
+      </c>
+      <c r="N14" s="82">
         <v>0</v>
       </c>
     </row>
@@ -8771,13 +8747,13 @@
       <c r="K15" s="69">
         <v>0</v>
       </c>
-      <c r="L15" s="70">
-        <v>0</v>
-      </c>
-      <c r="M15" s="70">
-        <v>0</v>
-      </c>
-      <c r="N15" s="71">
+      <c r="L15" s="69">
+        <v>0</v>
+      </c>
+      <c r="M15" s="69">
+        <v>0</v>
+      </c>
+      <c r="N15" s="70">
         <v>0</v>
       </c>
     </row>
@@ -8806,26 +8782,26 @@
       <c r="H16" s="25">
         <v>32</v>
       </c>
-      <c r="I16" s="72">
-        <v>0</v>
-      </c>
-      <c r="J16" s="73">
+      <c r="I16" s="71">
+        <v>0</v>
+      </c>
+      <c r="J16" s="72">
         <v>0</v>
       </c>
       <c r="K16" s="69">
         <v>0</v>
       </c>
-      <c r="L16" s="74">
-        <v>0</v>
-      </c>
-      <c r="M16" s="74">
-        <v>0</v>
-      </c>
-      <c r="N16" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="28.8" hidden="1" spans="1:14">
+      <c r="L16" s="73">
+        <v>0</v>
+      </c>
+      <c r="M16" s="73">
+        <v>0</v>
+      </c>
+      <c r="N16" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:14">
       <c r="A17" s="10" t="s">
         <v>51</v>
       </c>
@@ -8850,13 +8826,13 @@
       <c r="H17" s="28">
         <v>64</v>
       </c>
-      <c r="I17" s="85">
-        <v>1</v>
-      </c>
-      <c r="J17" s="86">
-        <v>0</v>
-      </c>
-      <c r="K17" s="87"/>
+      <c r="I17" s="83">
+        <v>1</v>
+      </c>
+      <c r="J17" s="84">
+        <v>0</v>
+      </c>
+      <c r="K17" s="34"/>
       <c r="L17" s="34">
         <v>1</v>
       </c>
@@ -8867,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="28.8" hidden="1" spans="1:14">
+    <row r="18" ht="28.8" spans="1:14">
       <c r="A18" s="10" t="s">
         <v>51</v>
       </c>
@@ -8892,13 +8868,13 @@
       <c r="H18" s="24">
         <v>78</v>
       </c>
-      <c r="I18" s="88">
+      <c r="I18" s="85">
         <v>4</v>
       </c>
-      <c r="J18" s="89">
+      <c r="J18" s="86">
         <v>2</v>
       </c>
-      <c r="K18" s="90"/>
+      <c r="K18" s="24"/>
       <c r="L18" s="24">
         <v>1</v>
       </c>
@@ -8909,7 +8885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="28.8" hidden="1" spans="1:14">
+    <row r="19" ht="28.8" spans="1:14">
       <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
@@ -8934,17 +8910,17 @@
       <c r="H19" s="24">
         <v>88</v>
       </c>
-      <c r="I19" s="91">
+      <c r="I19" s="87">
         <v>2</v>
       </c>
-      <c r="J19" s="92">
+      <c r="J19" s="88">
         <v>2</v>
       </c>
-      <c r="K19" s="93"/>
-      <c r="L19" s="94">
-        <v>0</v>
-      </c>
-      <c r="M19" s="94">
+      <c r="K19" s="89"/>
+      <c r="L19" s="89">
+        <v>0</v>
+      </c>
+      <c r="M19" s="89">
         <v>0</v>
       </c>
       <c r="N19" s="38">
@@ -8985,13 +8961,13 @@
       <c r="K20" s="69">
         <v>0</v>
       </c>
-      <c r="L20" s="70">
-        <v>1</v>
-      </c>
-      <c r="M20" s="70">
-        <v>0</v>
-      </c>
-      <c r="N20" s="71">
+      <c r="L20" s="69">
+        <v>1</v>
+      </c>
+      <c r="M20" s="69">
+        <v>0</v>
+      </c>
+      <c r="N20" s="70">
         <v>1</v>
       </c>
     </row>
@@ -9029,17 +9005,17 @@
       <c r="K21" s="69">
         <v>0</v>
       </c>
-      <c r="L21" s="70">
-        <v>0</v>
-      </c>
-      <c r="M21" s="70">
+      <c r="L21" s="69">
+        <v>0</v>
+      </c>
+      <c r="M21" s="69">
         <v>3</v>
       </c>
-      <c r="N21" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="28.8" spans="1:14">
+      <c r="N21" s="70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="29.55" spans="1:14">
       <c r="A22" s="10" t="s">
         <v>51</v>
       </c>
@@ -9073,17 +9049,17 @@
       <c r="K22" s="69">
         <v>0</v>
       </c>
-      <c r="L22" s="70">
-        <v>0</v>
-      </c>
-      <c r="M22" s="70">
+      <c r="L22" s="69">
+        <v>0</v>
+      </c>
+      <c r="M22" s="69">
         <v>5</v>
       </c>
-      <c r="N22" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="29.55" hidden="1" spans="1:14">
+      <c r="N22" s="70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="29.55" spans="1:14">
       <c r="A23" s="29" t="s">
         <v>65</v>
       </c>
@@ -9108,13 +9084,13 @@
       <c r="H23" s="34">
         <v>64</v>
       </c>
-      <c r="I23" s="95">
-        <v>1</v>
-      </c>
-      <c r="J23" s="96">
-        <v>0</v>
-      </c>
-      <c r="K23" s="97"/>
+      <c r="I23" s="90">
+        <v>1</v>
+      </c>
+      <c r="J23" s="91">
+        <v>0</v>
+      </c>
+      <c r="K23" s="57"/>
       <c r="L23" s="57">
         <v>1</v>
       </c>
@@ -9125,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:14">
+    <row r="24" spans="1:14">
       <c r="A24" s="2" t="s">
         <v>67</v>
       </c>
@@ -9150,13 +9126,13 @@
       <c r="H24" s="35">
         <v>64</v>
       </c>
-      <c r="I24" s="85">
+      <c r="I24" s="83">
         <v>2</v>
       </c>
-      <c r="J24" s="86">
-        <v>1</v>
-      </c>
-      <c r="K24" s="87"/>
+      <c r="J24" s="84">
+        <v>1</v>
+      </c>
+      <c r="K24" s="34"/>
       <c r="L24" s="34">
         <v>1</v>
       </c>
@@ -9167,7 +9143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:14">
+    <row r="25" spans="1:14">
       <c r="A25" s="17" t="s">
         <v>67</v>
       </c>
@@ -9192,17 +9168,17 @@
       <c r="H25" s="38">
         <v>99</v>
       </c>
-      <c r="I25" s="91">
+      <c r="I25" s="87">
         <v>6</v>
       </c>
-      <c r="J25" s="92">
-        <v>1</v>
-      </c>
-      <c r="K25" s="93"/>
-      <c r="L25" s="94">
+      <c r="J25" s="88">
+        <v>1</v>
+      </c>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89">
         <v>3</v>
       </c>
-      <c r="M25" s="94">
+      <c r="M25" s="89">
         <v>2</v>
       </c>
       <c r="N25" s="38">
@@ -9243,13 +9219,13 @@
       <c r="K26" s="69">
         <v>0</v>
       </c>
-      <c r="L26" s="70">
-        <v>0</v>
-      </c>
-      <c r="M26" s="70">
-        <v>0</v>
-      </c>
-      <c r="N26" s="71">
+      <c r="L26" s="69">
+        <v>0</v>
+      </c>
+      <c r="M26" s="69">
+        <v>0</v>
+      </c>
+      <c r="N26" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9287,13 +9263,13 @@
       <c r="K27" s="69">
         <v>0</v>
       </c>
-      <c r="L27" s="70">
-        <v>0</v>
-      </c>
-      <c r="M27" s="70">
-        <v>0</v>
-      </c>
-      <c r="N27" s="71">
+      <c r="L27" s="69">
+        <v>0</v>
+      </c>
+      <c r="M27" s="69">
+        <v>0</v>
+      </c>
+      <c r="N27" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9331,13 +9307,13 @@
       <c r="K28" s="69">
         <v>0</v>
       </c>
-      <c r="L28" s="70">
-        <v>1</v>
-      </c>
-      <c r="M28" s="70">
-        <v>0</v>
-      </c>
-      <c r="N28" s="71">
+      <c r="L28" s="69">
+        <v>1</v>
+      </c>
+      <c r="M28" s="69">
+        <v>0</v>
+      </c>
+      <c r="N28" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9375,13 +9351,13 @@
       <c r="K29" s="69">
         <v>0</v>
       </c>
-      <c r="L29" s="70">
-        <v>1</v>
-      </c>
-      <c r="M29" s="70">
-        <v>1</v>
-      </c>
-      <c r="N29" s="71">
+      <c r="L29" s="69">
+        <v>1</v>
+      </c>
+      <c r="M29" s="69">
+        <v>1</v>
+      </c>
+      <c r="N29" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9410,26 +9386,26 @@
       <c r="H30" s="40">
         <v>32</v>
       </c>
-      <c r="I30" s="72">
-        <v>1</v>
-      </c>
-      <c r="J30" s="73">
+      <c r="I30" s="71">
+        <v>1</v>
+      </c>
+      <c r="J30" s="72">
         <v>1</v>
       </c>
       <c r="K30" s="69">
         <v>0</v>
       </c>
-      <c r="L30" s="74">
-        <v>0</v>
-      </c>
-      <c r="M30" s="74">
-        <v>0</v>
-      </c>
-      <c r="N30" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="28.8" hidden="1" spans="1:14">
+      <c r="L30" s="73">
+        <v>0</v>
+      </c>
+      <c r="M30" s="73">
+        <v>0</v>
+      </c>
+      <c r="N30" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:14">
       <c r="A31" s="9" t="s">
         <v>78</v>
       </c>
@@ -9454,13 +9430,13 @@
       <c r="H31" s="35">
         <v>64</v>
       </c>
-      <c r="I31" s="85">
-        <v>1</v>
-      </c>
-      <c r="J31" s="86">
-        <v>1</v>
-      </c>
-      <c r="K31" s="87"/>
+      <c r="I31" s="83">
+        <v>1</v>
+      </c>
+      <c r="J31" s="84">
+        <v>1</v>
+      </c>
+      <c r="K31" s="34"/>
       <c r="L31" s="34">
         <v>0</v>
       </c>
@@ -9471,7 +9447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="29.55" hidden="1" spans="1:14">
+    <row r="32" ht="29.55" spans="1:14">
       <c r="A32" s="14" t="s">
         <v>78</v>
       </c>
@@ -9496,13 +9472,13 @@
       <c r="H32" s="44">
         <v>100</v>
       </c>
-      <c r="I32" s="88">
-        <v>0</v>
-      </c>
-      <c r="J32" s="89">
-        <v>0</v>
-      </c>
-      <c r="K32" s="90"/>
+      <c r="I32" s="85">
+        <v>0</v>
+      </c>
+      <c r="J32" s="86">
+        <v>0</v>
+      </c>
+      <c r="K32" s="24"/>
       <c r="L32" s="24">
         <v>0</v>
       </c>
@@ -9513,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="28.8" hidden="1" spans="1:14">
+    <row r="33" ht="28.8" spans="1:14">
       <c r="A33" s="10" t="s">
         <v>80</v>
       </c>
@@ -9538,13 +9514,13 @@
       <c r="H33" s="38">
         <v>64</v>
       </c>
-      <c r="I33" s="80">
+      <c r="I33" s="79">
         <v>3</v>
       </c>
-      <c r="J33" s="81">
-        <v>1</v>
-      </c>
-      <c r="K33" s="82"/>
+      <c r="J33" s="80">
+        <v>1</v>
+      </c>
+      <c r="K33" s="23"/>
       <c r="L33" s="23">
         <v>0</v>
       </c>
@@ -9589,13 +9565,13 @@
       <c r="K34" s="69">
         <v>0</v>
       </c>
-      <c r="L34" s="70">
-        <v>0</v>
-      </c>
-      <c r="M34" s="70">
-        <v>0</v>
-      </c>
-      <c r="N34" s="71">
+      <c r="L34" s="69">
+        <v>0</v>
+      </c>
+      <c r="M34" s="69">
+        <v>0</v>
+      </c>
+      <c r="N34" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9633,13 +9609,13 @@
       <c r="K35" s="69">
         <v>0</v>
       </c>
-      <c r="L35" s="70">
-        <v>0</v>
-      </c>
-      <c r="M35" s="70">
-        <v>0</v>
-      </c>
-      <c r="N35" s="71">
+      <c r="L35" s="69">
+        <v>0</v>
+      </c>
+      <c r="M35" s="69">
+        <v>0</v>
+      </c>
+      <c r="N35" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9668,22 +9644,22 @@
       <c r="H36" s="44">
         <v>32</v>
       </c>
-      <c r="I36" s="72">
-        <v>0</v>
-      </c>
-      <c r="J36" s="73">
+      <c r="I36" s="71">
+        <v>0</v>
+      </c>
+      <c r="J36" s="72">
         <v>0</v>
       </c>
       <c r="K36" s="69">
         <v>0</v>
       </c>
-      <c r="L36" s="74">
-        <v>0</v>
-      </c>
-      <c r="M36" s="74">
-        <v>0</v>
-      </c>
-      <c r="N36" s="79">
+      <c r="L36" s="73">
+        <v>0</v>
+      </c>
+      <c r="M36" s="73">
+        <v>0</v>
+      </c>
+      <c r="N36" s="78">
         <v>0</v>
       </c>
     </row>
@@ -9712,22 +9688,22 @@
       <c r="H37" s="35">
         <v>32</v>
       </c>
-      <c r="I37" s="75">
-        <v>0</v>
-      </c>
-      <c r="J37" s="76">
+      <c r="I37" s="74">
+        <v>0</v>
+      </c>
+      <c r="J37" s="75">
         <v>0</v>
       </c>
       <c r="K37" s="69">
         <v>0</v>
       </c>
-      <c r="L37" s="77">
-        <v>0</v>
-      </c>
-      <c r="M37" s="77">
-        <v>0</v>
-      </c>
-      <c r="N37" s="78">
+      <c r="L37" s="76">
+        <v>0</v>
+      </c>
+      <c r="M37" s="76">
+        <v>0</v>
+      </c>
+      <c r="N37" s="77">
         <v>0</v>
       </c>
     </row>
@@ -9765,13 +9741,13 @@
       <c r="K38" s="69">
         <v>0</v>
       </c>
-      <c r="L38" s="70">
-        <v>0</v>
-      </c>
-      <c r="M38" s="70">
-        <v>0</v>
-      </c>
-      <c r="N38" s="71">
+      <c r="L38" s="69">
+        <v>0</v>
+      </c>
+      <c r="M38" s="69">
+        <v>0</v>
+      </c>
+      <c r="N38" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9800,26 +9776,26 @@
       <c r="H39" s="40">
         <v>32</v>
       </c>
-      <c r="I39" s="72">
-        <v>0</v>
-      </c>
-      <c r="J39" s="73">
+      <c r="I39" s="71">
+        <v>0</v>
+      </c>
+      <c r="J39" s="72">
         <v>0</v>
       </c>
       <c r="K39" s="69">
         <v>0</v>
       </c>
-      <c r="L39" s="74">
-        <v>0</v>
-      </c>
-      <c r="M39" s="74">
-        <v>0</v>
-      </c>
-      <c r="N39" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="28.8" hidden="1" spans="1:14">
+      <c r="L39" s="73">
+        <v>0</v>
+      </c>
+      <c r="M39" s="73">
+        <v>0</v>
+      </c>
+      <c r="N39" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="28.8" spans="1:14">
       <c r="A40" s="9" t="s">
         <v>87</v>
       </c>
@@ -9844,13 +9820,13 @@
       <c r="H40" s="49">
         <v>64</v>
       </c>
-      <c r="I40" s="80">
+      <c r="I40" s="79">
         <v>3</v>
       </c>
-      <c r="J40" s="81">
+      <c r="J40" s="80">
         <v>3</v>
       </c>
-      <c r="K40" s="82"/>
+      <c r="K40" s="23"/>
       <c r="L40" s="23">
         <v>0</v>
       </c>
@@ -9895,13 +9871,13 @@
       <c r="K41" s="69">
         <v>0</v>
       </c>
-      <c r="L41" s="70">
-        <v>0</v>
-      </c>
-      <c r="M41" s="70">
-        <v>0</v>
-      </c>
-      <c r="N41" s="71">
+      <c r="L41" s="69">
+        <v>0</v>
+      </c>
+      <c r="M41" s="69">
+        <v>0</v>
+      </c>
+      <c r="N41" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9939,13 +9915,13 @@
       <c r="K42" s="69">
         <v>0</v>
       </c>
-      <c r="L42" s="70">
-        <v>0</v>
-      </c>
-      <c r="M42" s="70">
-        <v>0</v>
-      </c>
-      <c r="N42" s="71">
+      <c r="L42" s="69">
+        <v>0</v>
+      </c>
+      <c r="M42" s="69">
+        <v>0</v>
+      </c>
+      <c r="N42" s="70">
         <v>0</v>
       </c>
     </row>
@@ -9974,31 +9950,31 @@
       <c r="H43" s="44">
         <v>32</v>
       </c>
-      <c r="I43" s="72">
-        <v>1</v>
-      </c>
-      <c r="J43" s="73">
+      <c r="I43" s="71">
+        <v>1</v>
+      </c>
+      <c r="J43" s="72">
         <v>0</v>
       </c>
       <c r="K43" s="69">
         <v>0</v>
       </c>
-      <c r="L43" s="74">
-        <v>1</v>
-      </c>
-      <c r="M43" s="74">
-        <v>0</v>
-      </c>
-      <c r="N43" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="29.55" hidden="1" spans="1:14">
+      <c r="L43" s="73">
+        <v>1</v>
+      </c>
+      <c r="M43" s="73">
+        <v>0</v>
+      </c>
+      <c r="N43" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="29.55" spans="1:14">
       <c r="A44" s="29" t="s">
         <v>91</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C44" s="31">
         <v>59.577677</v>
@@ -10018,13 +9994,13 @@
       <c r="H44" s="58">
         <v>64</v>
       </c>
-      <c r="I44" s="95">
+      <c r="I44" s="90">
         <v>6</v>
       </c>
-      <c r="J44" s="96">
+      <c r="J44" s="91">
         <v>3</v>
       </c>
-      <c r="K44" s="97"/>
+      <c r="K44" s="57"/>
       <c r="L44" s="57">
         <v>2</v>
       </c>
@@ -10060,22 +10036,22 @@
       <c r="H45" s="40">
         <v>32</v>
       </c>
-      <c r="I45" s="75">
-        <v>0</v>
-      </c>
-      <c r="J45" s="76">
+      <c r="I45" s="74">
+        <v>0</v>
+      </c>
+      <c r="J45" s="75">
         <v>0</v>
       </c>
       <c r="K45" s="69">
         <v>0</v>
       </c>
-      <c r="L45" s="77">
-        <v>0</v>
-      </c>
-      <c r="M45" s="77">
-        <v>0</v>
-      </c>
-      <c r="N45" s="78">
+      <c r="L45" s="76">
+        <v>0</v>
+      </c>
+      <c r="M45" s="76">
+        <v>0</v>
+      </c>
+      <c r="N45" s="77">
         <v>0</v>
       </c>
     </row>
@@ -10113,13 +10089,13 @@
       <c r="K46" s="69">
         <v>0</v>
       </c>
-      <c r="L46" s="70">
+      <c r="L46" s="69">
         <v>2</v>
       </c>
-      <c r="M46" s="70">
-        <v>1</v>
-      </c>
-      <c r="N46" s="71">
+      <c r="M46" s="69">
+        <v>1</v>
+      </c>
+      <c r="N46" s="70">
         <v>0</v>
       </c>
     </row>
@@ -10148,22 +10124,22 @@
       <c r="H47" s="44">
         <v>32</v>
       </c>
-      <c r="I47" s="72">
-        <v>1</v>
-      </c>
-      <c r="J47" s="73">
+      <c r="I47" s="71">
+        <v>1</v>
+      </c>
+      <c r="J47" s="72">
         <v>1</v>
       </c>
       <c r="K47" s="69">
         <v>0</v>
       </c>
-      <c r="L47" s="74">
-        <v>0</v>
-      </c>
-      <c r="M47" s="74">
-        <v>0</v>
-      </c>
-      <c r="N47" s="79">
+      <c r="L47" s="73">
+        <v>0</v>
+      </c>
+      <c r="M47" s="73">
+        <v>0</v>
+      </c>
+      <c r="N47" s="78">
         <v>0</v>
       </c>
     </row>
@@ -10192,20 +10168,20 @@
       <c r="H48" s="35">
         <v>32</v>
       </c>
-      <c r="I48" s="75">
+      <c r="I48" s="74">
         <v>4</v>
       </c>
-      <c r="J48" s="76">
+      <c r="J48" s="75">
         <v>4</v>
       </c>
-      <c r="K48" s="98"/>
-      <c r="L48" s="77">
-        <v>0</v>
-      </c>
-      <c r="M48" s="77">
-        <v>0</v>
-      </c>
-      <c r="N48" s="78">
+      <c r="K48" s="76"/>
+      <c r="L48" s="76">
+        <v>0</v>
+      </c>
+      <c r="M48" s="76">
+        <v>0</v>
+      </c>
+      <c r="N48" s="77">
         <v>0</v>
       </c>
     </row>
@@ -10241,13 +10217,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="69"/>
-      <c r="L49" s="70">
-        <v>1</v>
-      </c>
-      <c r="M49" s="70">
-        <v>0</v>
-      </c>
-      <c r="N49" s="71">
+      <c r="L49" s="69">
+        <v>1</v>
+      </c>
+      <c r="M49" s="69">
+        <v>0</v>
+      </c>
+      <c r="N49" s="70">
         <v>0</v>
       </c>
     </row>
@@ -10276,22 +10252,22 @@
       <c r="H50" s="44">
         <v>32</v>
       </c>
-      <c r="I50" s="72">
+      <c r="I50" s="71">
         <v>2</v>
       </c>
-      <c r="J50" s="73">
-        <v>1</v>
-      </c>
-      <c r="K50" s="99">
-        <v>1</v>
-      </c>
-      <c r="L50" s="74">
-        <v>0</v>
-      </c>
-      <c r="M50" s="74">
-        <v>0</v>
-      </c>
-      <c r="N50" s="79">
+      <c r="J50" s="72">
+        <v>1</v>
+      </c>
+      <c r="K50" s="73">
+        <v>1</v>
+      </c>
+      <c r="L50" s="73">
+        <v>0</v>
+      </c>
+      <c r="M50" s="73">
+        <v>0</v>
+      </c>
+      <c r="N50" s="78">
         <v>0</v>
       </c>
     </row>
@@ -10320,22 +10296,22 @@
       <c r="H51" s="35">
         <v>32</v>
       </c>
-      <c r="I51" s="75">
+      <c r="I51" s="74">
         <v>6</v>
       </c>
-      <c r="J51" s="76">
+      <c r="J51" s="75">
         <v>3</v>
       </c>
-      <c r="K51" s="98">
-        <v>1</v>
-      </c>
-      <c r="L51" s="77">
-        <v>0</v>
-      </c>
-      <c r="M51" s="77">
+      <c r="K51" s="76">
+        <v>1</v>
+      </c>
+      <c r="L51" s="76">
+        <v>0</v>
+      </c>
+      <c r="M51" s="76">
         <v>2</v>
       </c>
-      <c r="N51" s="78">
+      <c r="N51" s="77">
         <v>0</v>
       </c>
     </row>
@@ -10373,13 +10349,13 @@
       <c r="K52" s="69">
         <v>0</v>
       </c>
-      <c r="L52" s="70">
-        <v>1</v>
-      </c>
-      <c r="M52" s="70">
-        <v>0</v>
-      </c>
-      <c r="N52" s="71">
+      <c r="L52" s="69">
+        <v>1</v>
+      </c>
+      <c r="M52" s="69">
+        <v>0</v>
+      </c>
+      <c r="N52" s="70">
         <v>0</v>
       </c>
     </row>
@@ -10408,22 +10384,22 @@
       <c r="H53" s="44">
         <v>32</v>
       </c>
-      <c r="I53" s="72">
+      <c r="I53" s="71">
         <v>3</v>
       </c>
-      <c r="J53" s="73">
+      <c r="J53" s="72">
         <v>3</v>
       </c>
       <c r="K53" s="69">
         <v>0</v>
       </c>
-      <c r="L53" s="74">
-        <v>0</v>
-      </c>
-      <c r="M53" s="74">
-        <v>0</v>
-      </c>
-      <c r="N53" s="79">
+      <c r="L53" s="73">
+        <v>0</v>
+      </c>
+      <c r="M53" s="73">
+        <v>0</v>
+      </c>
+      <c r="N53" s="78">
         <v>0</v>
       </c>
     </row>
@@ -10452,22 +10428,22 @@
       <c r="H54" s="35">
         <v>32</v>
       </c>
-      <c r="I54" s="75">
+      <c r="I54" s="74">
         <v>2</v>
       </c>
-      <c r="J54" s="76">
+      <c r="J54" s="75">
         <v>0</v>
       </c>
       <c r="K54" s="69">
         <v>0</v>
       </c>
-      <c r="L54" s="77">
+      <c r="L54" s="76">
         <v>2</v>
       </c>
-      <c r="M54" s="77">
-        <v>0</v>
-      </c>
-      <c r="N54" s="78">
+      <c r="M54" s="76">
+        <v>0</v>
+      </c>
+      <c r="N54" s="77">
         <v>0</v>
       </c>
     </row>
@@ -10505,13 +10481,13 @@
       <c r="K55" s="69">
         <v>0</v>
       </c>
-      <c r="L55" s="70">
-        <v>1</v>
-      </c>
-      <c r="M55" s="70">
-        <v>0</v>
-      </c>
-      <c r="N55" s="71">
+      <c r="L55" s="69">
+        <v>1</v>
+      </c>
+      <c r="M55" s="69">
+        <v>0</v>
+      </c>
+      <c r="N55" s="70">
         <v>0</v>
       </c>
     </row>
@@ -10540,22 +10516,22 @@
       <c r="H56" s="44">
         <v>32</v>
       </c>
-      <c r="I56" s="72">
+      <c r="I56" s="71">
         <v>5</v>
       </c>
-      <c r="J56" s="73">
+      <c r="J56" s="72">
         <v>1</v>
       </c>
       <c r="K56" s="69">
         <v>0</v>
       </c>
-      <c r="L56" s="74">
+      <c r="L56" s="73">
         <v>2</v>
       </c>
-      <c r="M56" s="74">
-        <v>0</v>
-      </c>
-      <c r="N56" s="79">
+      <c r="M56" s="73">
+        <v>0</v>
+      </c>
+      <c r="N56" s="78">
         <v>1</v>
       </c>
     </row>
@@ -10584,22 +10560,22 @@
       <c r="H57" s="35">
         <v>32</v>
       </c>
-      <c r="I57" s="75">
+      <c r="I57" s="74">
         <v>6</v>
       </c>
-      <c r="J57" s="76">
+      <c r="J57" s="75">
         <v>3</v>
       </c>
       <c r="K57" s="69">
         <v>0</v>
       </c>
-      <c r="L57" s="77">
+      <c r="L57" s="76">
         <v>2</v>
       </c>
-      <c r="M57" s="77">
-        <v>1</v>
-      </c>
-      <c r="N57" s="78">
+      <c r="M57" s="76">
+        <v>1</v>
+      </c>
+      <c r="N57" s="77">
         <v>0</v>
       </c>
     </row>
@@ -10637,13 +10613,13 @@
       <c r="K58" s="69">
         <v>0</v>
       </c>
-      <c r="L58" s="70">
-        <v>0</v>
-      </c>
-      <c r="M58" s="70">
-        <v>1</v>
-      </c>
-      <c r="N58" s="71">
+      <c r="L58" s="69">
+        <v>0</v>
+      </c>
+      <c r="M58" s="69">
+        <v>1</v>
+      </c>
+      <c r="N58" s="70">
         <v>0</v>
       </c>
     </row>
@@ -10672,26 +10648,26 @@
       <c r="H59" s="40">
         <v>32</v>
       </c>
-      <c r="I59" s="100">
-        <v>0</v>
-      </c>
-      <c r="J59" s="73">
+      <c r="I59" s="92">
+        <v>0</v>
+      </c>
+      <c r="J59" s="72">
         <v>1</v>
       </c>
       <c r="K59" s="69">
         <v>0</v>
       </c>
-      <c r="L59" s="74">
-        <v>0</v>
-      </c>
-      <c r="M59" s="74">
-        <v>0</v>
-      </c>
-      <c r="N59" s="79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" hidden="1" spans="1:14">
+      <c r="L59" s="73">
+        <v>0</v>
+      </c>
+      <c r="M59" s="73">
+        <v>0</v>
+      </c>
+      <c r="N59" s="78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="2" t="s">
         <v>130</v>
       </c>
@@ -10716,24 +10692,24 @@
       <c r="H60" s="35">
         <v>64</v>
       </c>
-      <c r="I60" s="85">
+      <c r="I60" s="83">
         <v>2</v>
       </c>
-      <c r="J60" s="86">
-        <v>1</v>
-      </c>
-      <c r="K60" s="87"/>
+      <c r="J60" s="84">
+        <v>1</v>
+      </c>
+      <c r="K60" s="34"/>
       <c r="L60" s="34">
         <v>1</v>
       </c>
-      <c r="M60" s="101">
-        <v>0</v>
-      </c>
-      <c r="N60" s="102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" hidden="1" spans="1:14">
+      <c r="M60" s="93">
+        <v>0</v>
+      </c>
+      <c r="N60" s="94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="17" t="s">
         <v>130</v>
       </c>
@@ -10758,13 +10734,13 @@
       <c r="H61" s="40">
         <v>60</v>
       </c>
-      <c r="I61" s="88">
+      <c r="I61" s="85">
         <v>12</v>
       </c>
-      <c r="J61" s="89">
+      <c r="J61" s="86">
         <v>9</v>
       </c>
-      <c r="K61" s="90"/>
+      <c r="K61" s="24"/>
       <c r="L61" s="24">
         <v>2</v>
       </c>
@@ -10775,7 +10751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:14">
+    <row r="62" spans="1:14">
       <c r="A62" s="17" t="s">
         <v>130</v>
       </c>
@@ -10800,20 +10776,20 @@
       <c r="H62" s="38">
         <v>70</v>
       </c>
-      <c r="I62" s="91">
+      <c r="I62" s="87">
         <v>5</v>
       </c>
-      <c r="J62" s="92">
+      <c r="J62" s="88">
         <v>2</v>
       </c>
-      <c r="K62" s="93"/>
-      <c r="L62" s="94">
-        <v>1</v>
-      </c>
-      <c r="M62" s="103">
+      <c r="K62" s="89"/>
+      <c r="L62" s="89">
+        <v>1</v>
+      </c>
+      <c r="M62" s="95">
         <v>2</v>
       </c>
-      <c r="N62" s="104">
+      <c r="N62" s="96">
         <v>0</v>
       </c>
     </row>
@@ -10842,22 +10818,22 @@
       <c r="H63" s="64">
         <v>53</v>
       </c>
-      <c r="I63" s="105">
+      <c r="I63" s="97">
         <v>5</v>
       </c>
-      <c r="J63" s="106">
+      <c r="J63" s="98">
         <v>1</v>
       </c>
       <c r="K63" s="69">
         <v>0</v>
       </c>
-      <c r="L63" s="107">
+      <c r="L63" s="99">
         <v>3</v>
       </c>
-      <c r="M63" s="107">
-        <v>1</v>
-      </c>
-      <c r="N63" s="108">
+      <c r="M63" s="99">
+        <v>1</v>
+      </c>
+      <c r="N63" s="100">
         <v>0</v>
       </c>
     </row>
@@ -10886,22 +10862,22 @@
       <c r="H64" s="64">
         <v>54</v>
       </c>
-      <c r="I64" s="105">
+      <c r="I64" s="97">
         <v>3</v>
       </c>
-      <c r="J64" s="106">
+      <c r="J64" s="98">
         <v>1</v>
       </c>
       <c r="K64" s="69">
         <v>0</v>
       </c>
-      <c r="L64" s="107">
-        <v>0</v>
-      </c>
-      <c r="M64" s="107">
-        <v>1</v>
-      </c>
-      <c r="N64" s="108">
+      <c r="L64" s="99">
+        <v>0</v>
+      </c>
+      <c r="M64" s="99">
+        <v>1</v>
+      </c>
+      <c r="N64" s="100">
         <v>0</v>
       </c>
     </row>
@@ -10927,29 +10903,29 @@
       <c r="G65" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H65" s="109">
+      <c r="H65" s="101">
         <v>41</v>
       </c>
-      <c r="I65" s="115">
+      <c r="I65" s="107">
         <v>4</v>
       </c>
-      <c r="J65" s="116">
+      <c r="J65" s="108">
         <v>4</v>
       </c>
       <c r="K65" s="69">
         <v>0</v>
       </c>
-      <c r="L65" s="117">
-        <v>0</v>
-      </c>
-      <c r="M65" s="117">
-        <v>0</v>
-      </c>
-      <c r="N65" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="29.55" hidden="1" spans="1:14">
+      <c r="L65" s="109">
+        <v>0</v>
+      </c>
+      <c r="M65" s="109">
+        <v>0</v>
+      </c>
+      <c r="N65" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="29.55" spans="1:14">
       <c r="A66" s="29" t="s">
         <v>140</v>
       </c>
@@ -10959,10 +10935,10 @@
       <c r="C66" s="55">
         <v>59.56098</v>
       </c>
-      <c r="D66" s="110">
+      <c r="D66" s="102">
         <v>150.924676</v>
       </c>
-      <c r="E66" s="111">
+      <c r="E66" s="103">
         <v>2021</v>
       </c>
       <c r="F66" s="56">
@@ -10971,40 +10947,40 @@
       <c r="G66" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="H66" s="110">
+      <c r="H66" s="102">
         <v>64</v>
       </c>
-      <c r="I66" s="111">
-        <v>1</v>
-      </c>
-      <c r="J66" s="119">
-        <v>1</v>
-      </c>
-      <c r="K66" s="120"/>
+      <c r="I66" s="103">
+        <v>1</v>
+      </c>
+      <c r="J66" s="111">
+        <v>1</v>
+      </c>
+      <c r="K66" s="55"/>
       <c r="L66" s="55">
         <v>0</v>
       </c>
       <c r="M66" s="55">
         <v>0</v>
       </c>
-      <c r="N66" s="110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="15.15" hidden="1" spans="1:14">
-      <c r="A67" s="112" t="s">
+      <c r="N66" s="102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.15" spans="1:14">
+      <c r="A67" s="104" t="s">
         <v>142</v>
       </c>
-      <c r="B67" s="113" t="s">
+      <c r="B67" s="105" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="113">
+      <c r="C67" s="105">
         <v>59.558174</v>
       </c>
-      <c r="D67" s="114">
+      <c r="D67" s="106">
         <v>150.929357</v>
       </c>
-      <c r="E67" s="111">
+      <c r="E67" s="103">
         <v>2021</v>
       </c>
       <c r="F67" s="56">
@@ -11013,33 +10989,28 @@
       <c r="G67" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="110">
+      <c r="H67" s="102">
         <v>64</v>
       </c>
-      <c r="I67" s="111">
+      <c r="I67" s="103">
         <v>2</v>
       </c>
-      <c r="J67" s="119">
-        <v>1</v>
-      </c>
-      <c r="K67" s="120"/>
+      <c r="J67" s="111">
+        <v>1</v>
+      </c>
+      <c r="K67" s="55"/>
       <c r="L67" s="55">
         <v>0</v>
       </c>
       <c r="M67" s="30">
         <v>0</v>
       </c>
-      <c r="N67" s="121">
+      <c r="N67" s="112">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N67" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="2023"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21996" windowHeight="8507" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9324" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table" sheetId="2" r:id="rId1"/>
@@ -8962,13 +8962,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="69">
         <v>0</v>
       </c>
       <c r="N20" s="70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="28.8" spans="1:14">
@@ -10532,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" ht="28.8" spans="1:14">

--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog.xlsx
@@ -8096,6 +8096,11 @@
   <cols>
     <col min="1" max="1" width="16.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="16.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.3333333333333" customWidth="1"/>
+    <col min="11" max="11" width="15.2222222222222" customWidth="1"/>
+    <col min="12" max="12" width="12.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="11.6666666666667" customWidth="1"/>
     <col min="14" max="14" width="11.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8143,7 +8148,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:14">
+    <row r="2" spans="1:14">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -8187,7 +8192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.15" hidden="1" spans="1:14">
+    <row r="3" ht="15.15" spans="1:14">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -8231,7 +8236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="28.8" hidden="1" spans="1:14">
+    <row r="4" ht="28.8" spans="1:14">
       <c r="A4" s="18" t="s">
         <v>31</v>
       </c>
@@ -8275,7 +8280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="28.8" hidden="1" spans="1:14">
+    <row r="5" ht="28.8" spans="1:14">
       <c r="A5" s="23" t="s">
         <v>31</v>
       </c>
@@ -8319,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="29.55" hidden="1" spans="1:14">
+    <row r="6" ht="29.55" spans="1:14">
       <c r="A6" s="27" t="s">
         <v>31</v>
       </c>
@@ -8363,7 +8368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:14">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
         <v>38</v>
       </c>
@@ -8407,7 +8412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:14">
+    <row r="8" spans="1:14">
       <c r="A8" s="31" t="s">
         <v>38</v>
       </c>
@@ -8451,7 +8456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15.15" hidden="1" spans="1:14">
+    <row r="9" ht="15.15" spans="1:14">
       <c r="A9" s="12" t="s">
         <v>38</v>
       </c>
@@ -8495,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="28.8" hidden="1" spans="1:14">
+    <row r="10" ht="28.8" spans="1:14">
       <c r="A10" s="18" t="s">
         <v>41</v>
       </c>
@@ -8539,7 +8544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="28.8" hidden="1" spans="1:14">
+    <row r="11" ht="28.8" spans="1:14">
       <c r="A11" s="23" t="s">
         <v>41</v>
       </c>
@@ -8583,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="29.55" hidden="1" spans="1:14">
+    <row r="12" ht="29.55" spans="1:14">
       <c r="A12" s="23" t="s">
         <v>41</v>
       </c>
@@ -8669,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="28.8" hidden="1" spans="1:14">
+    <row r="14" ht="28.8" spans="1:14">
       <c r="A14" s="23" t="s">
         <v>44</v>
       </c>
@@ -8713,7 +8718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="28.8" hidden="1" spans="1:14">
+    <row r="15" ht="28.8" spans="1:14">
       <c r="A15" s="23" t="s">
         <v>44</v>
       </c>
@@ -8757,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="29.55" hidden="1" spans="1:14">
+    <row r="16" ht="29.55" spans="1:14">
       <c r="A16" s="27" t="s">
         <v>44</v>
       </c>
@@ -8927,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="28.8" hidden="1" spans="1:14">
+    <row r="20" ht="28.8" spans="1:14">
       <c r="A20" s="23" t="s">
         <v>51</v>
       </c>
@@ -8971,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="28.8" hidden="1" spans="1:14">
+    <row r="21" ht="28.8" spans="1:14">
       <c r="A21" s="23" t="s">
         <v>51</v>
       </c>
@@ -9015,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="29.55" hidden="1" spans="1:14">
+    <row r="22" ht="28.8" spans="1:14">
       <c r="A22" s="23" t="s">
         <v>51</v>
       </c>
@@ -9101,7 +9106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" hidden="1" spans="1:14">
       <c r="A24" s="4" t="s">
         <v>67</v>
       </c>
@@ -9143,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" hidden="1" spans="1:14">
       <c r="A25" s="31" t="s">
         <v>67</v>
       </c>
@@ -9531,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="28.8" hidden="1" spans="1:14">
+    <row r="34" ht="28.8" spans="1:14">
       <c r="A34" s="23" t="s">
         <v>80</v>
       </c>
@@ -9575,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="28.8" hidden="1" spans="1:14">
+    <row r="35" ht="28.8" spans="1:14">
       <c r="A35" s="23" t="s">
         <v>80</v>
       </c>
@@ -9619,7 +9624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="29.55" hidden="1" spans="1:14">
+    <row r="36" ht="29.55" spans="1:14">
       <c r="A36" s="27" t="s">
         <v>80</v>
       </c>
@@ -9663,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:14">
+    <row r="37" spans="1:14">
       <c r="A37" s="4" t="s">
         <v>85</v>
       </c>
@@ -9707,7 +9712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:14">
+    <row r="38" spans="1:14">
       <c r="A38" s="31" t="s">
         <v>85</v>
       </c>
@@ -9751,7 +9756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="15.15" hidden="1" spans="1:14">
+    <row r="39" ht="15.15" spans="1:14">
       <c r="A39" s="31" t="s">
         <v>85</v>
       </c>
@@ -9837,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="28.8" hidden="1" spans="1:14">
+    <row r="41" ht="28.8" spans="1:14">
       <c r="A41" s="23" t="s">
         <v>87</v>
       </c>
@@ -9881,7 +9886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="28.8" hidden="1" spans="1:14">
+    <row r="42" ht="28.8" spans="1:14">
       <c r="A42" s="23" t="s">
         <v>87</v>
       </c>
@@ -9925,7 +9930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="29.55" hidden="1" spans="1:14">
+    <row r="43" ht="29.55" spans="1:14">
       <c r="A43" s="27" t="s">
         <v>87</v>
       </c>
@@ -10011,7 +10016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:14">
+    <row r="45" spans="1:14">
       <c r="A45" s="31" t="s">
         <v>95</v>
       </c>
@@ -10055,7 +10060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:14">
+    <row r="46" spans="1:14">
       <c r="A46" s="31" t="s">
         <v>95</v>
       </c>
@@ -10099,7 +10104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="15.15" hidden="1" spans="1:14">
+    <row r="47" ht="15.15" spans="1:14">
       <c r="A47" s="12" t="s">
         <v>95</v>
       </c>
@@ -10143,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:14">
+    <row r="48" spans="1:14">
       <c r="A48" s="4" t="s">
         <v>101</v>
       </c>
@@ -10172,9 +10177,11 @@
         <v>4</v>
       </c>
       <c r="J48" s="20">
-        <v>4</v>
-      </c>
-      <c r="K48" s="21"/>
+        <v>3</v>
+      </c>
+      <c r="K48" s="21">
+        <v>0</v>
+      </c>
       <c r="L48" s="21">
         <v>0</v>
       </c>
@@ -10185,7 +10192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:14">
+    <row r="49" spans="1:14">
       <c r="A49" s="31" t="s">
         <v>101</v>
       </c>
@@ -10216,7 +10223,9 @@
       <c r="J49" s="9">
         <v>0</v>
       </c>
-      <c r="K49" s="10"/>
+      <c r="K49" s="10">
+        <v>0</v>
+      </c>
       <c r="L49" s="10">
         <v>1</v>
       </c>
@@ -10227,7 +10236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="15.15" hidden="1" spans="1:14">
+    <row r="50" ht="15.15" spans="1:14">
       <c r="A50" s="12" t="s">
         <v>101</v>
       </c>
@@ -10256,10 +10265,10 @@
         <v>2</v>
       </c>
       <c r="J50" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="17">
         <v>0</v>
@@ -10271,7 +10280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="43.2" hidden="1" spans="1:14">
+    <row r="51" ht="43.2" spans="1:14">
       <c r="A51" s="18" t="s">
         <v>108</v>
       </c>
@@ -10303,10 +10312,10 @@
         <v>3</v>
       </c>
       <c r="K51" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="21">
         <v>2</v>
@@ -10315,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="43.2" hidden="1" spans="1:14">
+    <row r="52" ht="43.2" spans="1:14">
       <c r="A52" s="23" t="s">
         <v>108</v>
       </c>
@@ -10344,7 +10353,7 @@
         <v>2</v>
       </c>
       <c r="J52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="10">
         <v>0</v>
@@ -10359,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="43.95" hidden="1" spans="1:14">
+    <row r="53" ht="43.95" spans="1:14">
       <c r="A53" s="27" t="s">
         <v>108</v>
       </c>
@@ -10403,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:14">
+    <row r="54" spans="1:14">
       <c r="A54" s="4" t="s">
         <v>115</v>
       </c>
@@ -10447,7 +10456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:14">
+    <row r="55" spans="1:14">
       <c r="A55" s="31" t="s">
         <v>115</v>
       </c>
@@ -10491,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="15.15" hidden="1" spans="1:14">
+    <row r="56" ht="15.15" spans="1:14">
       <c r="A56" s="12" t="s">
         <v>115</v>
       </c>
@@ -10535,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" ht="28.8" hidden="1" spans="1:14">
+    <row r="57" ht="28.8" spans="1:14">
       <c r="A57" s="18" t="s">
         <v>122</v>
       </c>
@@ -10579,7 +10588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" ht="28.8" hidden="1" spans="1:14">
+    <row r="58" ht="28.8" spans="1:14">
       <c r="A58" s="23" t="s">
         <v>122</v>
       </c>
@@ -10623,7 +10632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="29.55" hidden="1" spans="1:14">
+    <row r="59" ht="29.55" spans="1:14">
       <c r="A59" s="23" t="s">
         <v>122</v>
       </c>
@@ -10793,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:14">
+    <row r="63" spans="1:14">
       <c r="A63" s="31" t="s">
         <v>130</v>
       </c>
@@ -10837,7 +10846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:14">
+    <row r="64" spans="1:14">
       <c r="A64" s="31" t="s">
         <v>130</v>
       </c>
@@ -10866,7 +10875,7 @@
         <v>3</v>
       </c>
       <c r="J64" s="98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="10">
         <v>0</v>
@@ -10875,13 +10884,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" s="100">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="15.15" hidden="1" spans="1:14">
+    <row r="65" ht="15.15" spans="1:14">
       <c r="A65" s="12" t="s">
         <v>130</v>
       </c>
@@ -11011,9 +11020,9 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N67" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
+    <filterColumn colId="4">
       <filters>
-        <filter val="KHOL"/>
+        <filter val="2023"/>
       </filters>
     </filterColumn>
     <extLst/>
